--- a/fixtures/product-prototype/workbooks/criminal-courts-2023-24-cube-2-normalized.xlsx
+++ b/fixtures/product-prototype/workbooks/criminal-courts-2023-24-cube-2-normalized.xlsx
@@ -16868,18 +16868,18 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63DDECB6-FFCE-4324-AFDF-E3CF7EF9B96E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{63DDECB6-FFCE-4324-AFDF-E3CF7EF9B96E}">
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:O234"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" zeroHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:J234"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" zeroHeight="1" ns3:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="51.1796875" customWidth="1"/>
     <col min="2" max="10" width="8.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="74" customFormat="1" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" s="74" customFormat="1" ht="5.0999999999999996" customHeight="1" ns3:dyDescent="0.25">
       <c r="A1" s="108" t="s">
         <v>232</v>
       </c>
@@ -16893,7 +16893,7 @@
       <c r="I1" s="108"/>
       <c r="J1" s="108"/>
     </row>
-    <row r="2" spans="1:15" s="86" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" s="86" customFormat="1" ht="60" customHeight="1" ns3:dyDescent="0.25">
       <c r="A2" s="96" t="s">
         <v>1</v>
       </c>
@@ -16906,13 +16906,8 @@
       <c r="H2" s="96"/>
       <c r="I2" s="96"/>
       <c r="J2" s="96"/>
-      <c r="K2" s="96"/>
-      <c r="L2" s="96"/>
-      <c r="M2" s="96"/>
-      <c r="N2" s="96"/>
-      <c r="O2" s="96"/>
-    </row>
-    <row r="3" spans="1:15" s="89" customFormat="1" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    </row>
+    <row r="3" s="89" customFormat="1" ht="36" customHeight="1" thickBot="1" ns3:dyDescent="0.45">
       <c r="A3" s="113" t="s">
         <v>129</v>
       </c>
@@ -16926,7 +16921,7 @@
       <c r="I3" s="113"/>
       <c r="J3" s="113"/>
     </row>
-    <row r="4" spans="1:15" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="4" ht="15" customHeight="1" thickTop="1" ns3:dyDescent="0.3">
       <c r="A4" t="s">
         <v>62</v>
       </c>
@@ -16958,7 +16953,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A5" s="47"/>
       <c r="B5" s="109" t="s">
         <v>63</v>
@@ -16972,7 +16967,7 @@
       <c r="I5" s="109"/>
       <c r="J5" s="109"/>
     </row>
-    <row r="6" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A6" s="48" t="s">
         <v>64</v>
       </c>
@@ -16986,7 +16981,7 @@
       <c r="I6" s="49"/>
       <c r="J6" s="49"/>
     </row>
-    <row r="7" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A7" s="50" t="s">
         <v>38</v>
       </c>
@@ -17018,7 +17013,7 @@
         <v>334190</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A8" s="50" t="s">
         <v>45</v>
       </c>
@@ -17050,7 +17045,7 @@
         <v>107125</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A9" s="50" t="s">
         <v>65</v>
       </c>
@@ -17082,7 +17077,7 @@
         <v>4200</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A10" s="50"/>
       <c r="B10" s="51"/>
       <c r="C10" s="51"/>
@@ -17094,7 +17089,7 @@
       <c r="I10" s="51"/>
       <c r="J10" s="51"/>
     </row>
-    <row r="11" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A11" s="52" t="s">
         <v>53</v>
       </c>
@@ -17108,7 +17103,7 @@
       <c r="I11" s="51"/>
       <c r="J11" s="51"/>
     </row>
-    <row r="12" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A12" s="53" t="s">
         <v>66</v>
       </c>
@@ -17140,7 +17135,7 @@
         <v>38460</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A13" s="53" t="s">
         <v>46</v>
       </c>
@@ -17172,7 +17167,7 @@
         <v>57805</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A14" s="53" t="s">
         <v>47</v>
       </c>
@@ -17204,7 +17199,7 @@
         <v>60810</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A15" s="53" t="s">
         <v>48</v>
       </c>
@@ -17236,7 +17231,7 @@
         <v>62660</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A16" s="53" t="s">
         <v>49</v>
       </c>
@@ -17268,7 +17263,7 @@
         <v>58408</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A17" s="53" t="s">
         <v>50</v>
       </c>
@@ -17300,7 +17295,7 @@
         <v>52363</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A18" s="53" t="s">
         <v>51</v>
       </c>
@@ -17332,7 +17327,7 @@
         <v>39022</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A19" s="53" t="s">
         <v>52</v>
       </c>
@@ -17364,7 +17359,7 @@
         <v>29839</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A20" s="53" t="s">
         <v>67</v>
       </c>
@@ -17396,7 +17391,7 @@
         <v>40396</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A21" s="50" t="s">
         <v>54</v>
       </c>
@@ -17428,7 +17423,7 @@
         <v>36.4</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A22" s="50" t="s">
         <v>55</v>
       </c>
@@ -17460,7 +17455,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="20"/>
       <c r="C23" s="20"/>
@@ -17472,7 +17467,7 @@
       <c r="I23" s="20"/>
       <c r="J23" s="20"/>
     </row>
-    <row r="24" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A24" s="48" t="s">
         <v>173</v>
       </c>
@@ -17486,7 +17481,7 @@
       <c r="I24" s="20"/>
       <c r="J24" s="20"/>
     </row>
-    <row r="25" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A25" s="50" t="s">
         <v>69</v>
       </c>
@@ -17518,7 +17513,7 @@
         <v>16.899999999999999</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A26" s="50" t="s">
         <v>70</v>
       </c>
@@ -17550,7 +17545,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -17562,7 +17557,7 @@
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
     </row>
-    <row r="28" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A28" s="73" t="s">
         <v>174</v>
       </c>
@@ -17576,7 +17571,7 @@
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
     </row>
-    <row r="29" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A29" s="50" t="s">
         <v>39</v>
       </c>
@@ -17608,7 +17603,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A30" s="50" t="s">
         <v>175</v>
       </c>
@@ -17640,7 +17635,7 @@
         <v>59908</v>
       </c>
     </row>
-    <row r="31" spans="1:10" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" s="6" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A31" s="57" t="s">
         <v>119</v>
       </c>
@@ -17672,7 +17667,7 @@
         <v>52226</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A32" s="50" t="s">
         <v>41</v>
       </c>
@@ -17704,7 +17699,7 @@
         <v>4614</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A33" s="18" t="s">
         <v>76</v>
       </c>
@@ -17736,7 +17731,7 @@
         <v>20722</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A34" s="18" t="s">
         <v>148</v>
       </c>
@@ -17768,7 +17763,7 @@
         <v>4639</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A35" s="18" t="s">
         <v>23</v>
       </c>
@@ -17800,7 +17795,7 @@
         <v>2848</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A36" s="18" t="s">
         <v>24</v>
       </c>
@@ -17832,7 +17827,7 @@
         <v>10712</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A37" s="18" t="s">
         <v>78</v>
       </c>
@@ -17864,7 +17859,7 @@
         <v>37897</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A38" s="18" t="s">
         <v>42</v>
       </c>
@@ -17896,7 +17891,7 @@
         <v>8189</v>
       </c>
     </row>
-    <row r="39" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A39" s="50" t="s">
         <v>43</v>
       </c>
@@ -17928,7 +17923,7 @@
         <v>35048</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A40" s="18" t="s">
         <v>30</v>
       </c>
@@ -17960,7 +17955,7 @@
         <v>12653</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A41" s="50" t="s">
         <v>31</v>
       </c>
@@ -17992,7 +17987,7 @@
         <v>14107</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A42" s="50" t="s">
         <v>44</v>
       </c>
@@ -18024,7 +18019,7 @@
         <v>16778</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A43" s="50" t="s">
         <v>176</v>
       </c>
@@ -18056,7 +18051,7 @@
         <v>165524</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A44" s="54" t="s">
         <v>177</v>
       </c>
@@ -18088,7 +18083,7 @@
         <v>44752</v>
       </c>
     </row>
-    <row r="45" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A45" s="50" t="s">
         <v>35</v>
       </c>
@@ -18120,7 +18115,7 @@
         <v>8352</v>
       </c>
     </row>
-    <row r="46" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A46" s="50"/>
       <c r="B46" s="51"/>
       <c r="C46" s="51"/>
@@ -18132,7 +18127,7 @@
       <c r="I46" s="51"/>
       <c r="J46" s="51"/>
     </row>
-    <row r="47" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A47" s="48" t="s">
         <v>89</v>
       </c>
@@ -18146,7 +18141,7 @@
       <c r="I47" s="55"/>
       <c r="J47" s="55"/>
     </row>
-    <row r="48" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A48" s="24" t="s">
         <v>90</v>
       </c>
@@ -18178,7 +18173,7 @@
         <v>44016</v>
       </c>
     </row>
-    <row r="49" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A49" s="24" t="s">
         <v>91</v>
       </c>
@@ -18210,7 +18205,7 @@
         <v>8981</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A50" s="24" t="s">
         <v>92</v>
       </c>
@@ -18242,7 +18237,7 @@
         <v>12722</v>
       </c>
     </row>
-    <row r="51" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A51" s="24" t="s">
         <v>93</v>
       </c>
@@ -18274,7 +18269,7 @@
         <v>11360</v>
       </c>
     </row>
-    <row r="52" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A52" s="24" t="s">
         <v>94</v>
       </c>
@@ -18306,7 +18301,7 @@
         <v>35793</v>
       </c>
     </row>
-    <row r="53" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A53" s="24" t="s">
         <v>178</v>
       </c>
@@ -18338,7 +18333,7 @@
         <v>237279</v>
       </c>
     </row>
-    <row r="54" spans="1:10" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" s="6" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A54" s="42" t="s">
         <v>179</v>
       </c>
@@ -18370,7 +18365,7 @@
         <v>233954</v>
       </c>
     </row>
-    <row r="55" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A55" s="24" t="s">
         <v>95</v>
       </c>
@@ -18402,7 +18397,7 @@
         <v>49927</v>
       </c>
     </row>
-    <row r="56" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A56" s="24" t="s">
         <v>96</v>
       </c>
@@ -18434,7 +18429,7 @@
         <v>46961</v>
       </c>
     </row>
-    <row r="57" spans="1:10" ht="25.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" ht="25.65" customHeight="1" ns3:dyDescent="0.3">
       <c r="A57" s="26" t="s">
         <v>202</v>
       </c>
@@ -18466,7 +18461,7 @@
         <v>447122</v>
       </c>
     </row>
-    <row r="58" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A58" s="47"/>
       <c r="B58" s="110" t="s">
         <v>97</v>
@@ -18480,7 +18475,7 @@
       <c r="I58" s="110"/>
       <c r="J58" s="110"/>
     </row>
-    <row r="59" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A59" s="48" t="s">
         <v>64</v>
       </c>
@@ -18494,7 +18489,7 @@
       <c r="I59" s="49"/>
       <c r="J59" s="49"/>
     </row>
-    <row r="60" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A60" s="50" t="s">
         <v>38</v>
       </c>
@@ -18526,7 +18521,7 @@
         <v>11035</v>
       </c>
     </row>
-    <row r="61" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A61" s="50" t="s">
         <v>45</v>
       </c>
@@ -18558,7 +18553,7 @@
         <v>1660</v>
       </c>
     </row>
-    <row r="62" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A62" s="50" t="s">
         <v>65</v>
       </c>
@@ -18590,7 +18585,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="63" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
       <c r="D63" s="1"/>
@@ -18601,7 +18596,7 @@
       <c r="I63" s="1"/>
       <c r="J63" s="1"/>
     </row>
-    <row r="64" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A64" s="52" t="s">
         <v>53</v>
       </c>
@@ -18615,7 +18610,7 @@
       <c r="I64" s="1"/>
       <c r="J64" s="1"/>
     </row>
-    <row r="65" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A65" s="53" t="s">
         <v>66</v>
       </c>
@@ -18647,7 +18642,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="66" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A66" s="53" t="s">
         <v>46</v>
       </c>
@@ -18679,7 +18674,7 @@
         <v>1848</v>
       </c>
     </row>
-    <row r="67" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A67" s="53" t="s">
         <v>47</v>
       </c>
@@ -18711,7 +18706,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="68" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A68" s="53" t="s">
         <v>48</v>
       </c>
@@ -18743,7 +18738,7 @@
         <v>2177</v>
       </c>
     </row>
-    <row r="69" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A69" s="53" t="s">
         <v>49</v>
       </c>
@@ -18775,7 +18770,7 @@
         <v>1854</v>
       </c>
     </row>
-    <row r="70" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A70" s="53" t="s">
         <v>50</v>
       </c>
@@ -18807,7 +18802,7 @@
         <v>1493</v>
       </c>
     </row>
-    <row r="71" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A71" s="53" t="s">
         <v>51</v>
       </c>
@@ -18839,7 +18834,7 @@
         <v>1015</v>
       </c>
     </row>
-    <row r="72" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A72" s="53" t="s">
         <v>52</v>
       </c>
@@ -18871,7 +18866,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="73" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A73" s="53" t="s">
         <v>67</v>
       </c>
@@ -18903,7 +18898,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="74" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A74" s="50" t="s">
         <v>54</v>
       </c>
@@ -18935,7 +18930,7 @@
         <v>36.799999999999997</v>
       </c>
     </row>
-    <row r="75" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A75" s="50" t="s">
         <v>55</v>
       </c>
@@ -18967,7 +18962,7 @@
         <v>34.6</v>
       </c>
     </row>
-    <row r="76" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A76" s="1"/>
       <c r="B76" s="20"/>
       <c r="C76" s="20"/>
@@ -18979,7 +18974,7 @@
       <c r="I76" s="20"/>
       <c r="J76" s="20"/>
     </row>
-    <row r="77" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A77" s="48" t="s">
         <v>173</v>
       </c>
@@ -18993,7 +18988,7 @@
       <c r="I77" s="20"/>
       <c r="J77" s="20"/>
     </row>
-    <row r="78" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A78" s="50" t="s">
         <v>69</v>
       </c>
@@ -19025,7 +19020,7 @@
         <v>51.2</v>
       </c>
     </row>
-    <row r="79" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A79" s="50" t="s">
         <v>70</v>
       </c>
@@ -19057,7 +19052,7 @@
         <v>37.9</v>
       </c>
     </row>
-    <row r="80" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
@@ -19069,7 +19064,7 @@
       <c r="I80" s="1"/>
       <c r="J80" s="1"/>
     </row>
-    <row r="81" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A81" s="73" t="s">
         <v>174</v>
       </c>
@@ -19083,7 +19078,7 @@
       <c r="I81" s="1"/>
       <c r="J81" s="1"/>
     </row>
-    <row r="82" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A82" s="50" t="s">
         <v>39</v>
       </c>
@@ -19115,7 +19110,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="83" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A83" s="50" t="s">
         <v>175</v>
       </c>
@@ -19147,7 +19142,7 @@
         <v>2536</v>
       </c>
     </row>
-    <row r="84" spans="1:10" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" s="6" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A84" s="57" t="s">
         <v>119</v>
       </c>
@@ -19179,7 +19174,7 @@
         <v>2363</v>
       </c>
     </row>
-    <row r="85" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A85" s="50" t="s">
         <v>41</v>
       </c>
@@ -19211,7 +19206,7 @@
         <v>2495</v>
       </c>
     </row>
-    <row r="86" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A86" s="18" t="s">
         <v>76</v>
       </c>
@@ -19243,7 +19238,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="87" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A87" s="18" t="s">
         <v>148</v>
       </c>
@@ -19275,7 +19270,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="88" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A88" s="18" t="s">
         <v>23</v>
       </c>
@@ -19307,7 +19302,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="89" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A89" s="18" t="s">
         <v>24</v>
       </c>
@@ -19339,7 +19334,7 @@
         <v>1071</v>
       </c>
     </row>
-    <row r="90" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A90" s="18" t="s">
         <v>78</v>
       </c>
@@ -19371,7 +19366,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="91" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A91" s="18" t="s">
         <v>42</v>
       </c>
@@ -19403,7 +19398,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="92" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A92" s="50" t="s">
         <v>43</v>
       </c>
@@ -19435,7 +19430,7 @@
         <v>2760</v>
       </c>
     </row>
-    <row r="93" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A93" s="18" t="s">
         <v>30</v>
       </c>
@@ -19467,7 +19462,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="94" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A94" s="50" t="s">
         <v>31</v>
       </c>
@@ -19499,7 +19494,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="95" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A95" s="50" t="s">
         <v>44</v>
       </c>
@@ -19531,7 +19526,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="96" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A96" s="50" t="s">
         <v>176</v>
       </c>
@@ -19563,7 +19558,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="97" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A97" s="54" t="s">
         <v>177</v>
       </c>
@@ -19595,7 +19590,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="98" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A98" s="50" t="s">
         <v>35</v>
       </c>
@@ -19627,7 +19622,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="99" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A99" s="50"/>
       <c r="B99" s="15"/>
       <c r="C99" s="15"/>
@@ -19639,7 +19634,7 @@
       <c r="I99" s="15"/>
       <c r="J99" s="15"/>
     </row>
-    <row r="100" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A100" s="48" t="s">
         <v>89</v>
       </c>
@@ -19653,7 +19648,7 @@
       <c r="I100" s="15"/>
       <c r="J100" s="15"/>
     </row>
-    <row r="101" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A101" s="24" t="s">
         <v>90</v>
       </c>
@@ -19685,7 +19680,7 @@
         <v>9286</v>
       </c>
     </row>
-    <row r="102" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A102" s="24" t="s">
         <v>91</v>
       </c>
@@ -19717,7 +19712,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="103" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A103" s="24" t="s">
         <v>92</v>
       </c>
@@ -19749,7 +19744,7 @@
         <v>1203</v>
       </c>
     </row>
-    <row r="104" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A104" s="24" t="s">
         <v>93</v>
       </c>
@@ -19781,7 +19776,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="105" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A105" s="24" t="s">
         <v>94</v>
       </c>
@@ -19813,7 +19808,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="106" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A106" s="24" t="s">
         <v>178</v>
       </c>
@@ -19845,7 +19840,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="107" spans="1:10" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" s="6" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A107" s="42" t="s">
         <v>179</v>
       </c>
@@ -19877,7 +19872,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="108" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A108" s="24" t="s">
         <v>95</v>
       </c>
@@ -19909,7 +19904,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="109" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A109" s="24" t="s">
         <v>96</v>
       </c>
@@ -19941,7 +19936,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="110" spans="1:10" ht="25.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" ht="25.65" customHeight="1" ns3:dyDescent="0.3">
       <c r="A110" s="26" t="s">
         <v>202</v>
       </c>
@@ -19973,7 +19968,7 @@
         <v>12763</v>
       </c>
     </row>
-    <row r="111" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A111" s="47"/>
       <c r="B111" s="110" t="s">
         <v>98</v>
@@ -19987,7 +19982,7 @@
       <c r="I111" s="110"/>
       <c r="J111" s="110"/>
     </row>
-    <row r="112" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A112" s="48" t="s">
         <v>64</v>
       </c>
@@ -20001,7 +19996,7 @@
       <c r="I112" s="49"/>
       <c r="J112" s="49"/>
     </row>
-    <row r="113" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A113" s="50" t="s">
         <v>38</v>
       </c>
@@ -20033,7 +20028,7 @@
         <v>308532</v>
       </c>
     </row>
-    <row r="114" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A114" s="50" t="s">
         <v>45</v>
       </c>
@@ -20065,7 +20060,7 @@
         <v>100425</v>
       </c>
     </row>
-    <row r="115" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A115" s="50" t="s">
         <v>65</v>
       </c>
@@ -20097,7 +20092,7 @@
         <v>4144</v>
       </c>
     </row>
-    <row r="116" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A116" s="50"/>
       <c r="B116" s="51"/>
       <c r="C116" s="51"/>
@@ -20109,7 +20104,7 @@
       <c r="I116" s="51"/>
       <c r="J116" s="51"/>
     </row>
-    <row r="117" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A117" s="52" t="s">
         <v>53</v>
       </c>
@@ -20123,7 +20118,7 @@
       <c r="I117" s="51"/>
       <c r="J117" s="51"/>
     </row>
-    <row r="118" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A118" s="53" t="s">
         <v>66</v>
       </c>
@@ -20155,7 +20150,7 @@
         <v>18428</v>
       </c>
     </row>
-    <row r="119" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A119" s="53" t="s">
         <v>46</v>
       </c>
@@ -20187,7 +20182,7 @@
         <v>55820</v>
       </c>
     </row>
-    <row r="120" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A120" s="53" t="s">
         <v>47</v>
       </c>
@@ -20219,7 +20214,7 @@
         <v>58781</v>
       </c>
     </row>
-    <row r="121" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A121" s="53" t="s">
         <v>48</v>
       </c>
@@ -20251,7 +20246,7 @@
         <v>60478</v>
       </c>
     </row>
-    <row r="122" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A122" s="53" t="s">
         <v>49</v>
       </c>
@@ -20283,7 +20278,7 @@
         <v>56546</v>
       </c>
     </row>
-    <row r="123" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A123" s="53" t="s">
         <v>50</v>
       </c>
@@ -20315,7 +20310,7 @@
         <v>50871</v>
       </c>
     </row>
-    <row r="124" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A124" s="53" t="s">
         <v>51</v>
       </c>
@@ -20347,7 +20342,7 @@
         <v>38002</v>
       </c>
     </row>
-    <row r="125" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A125" s="53" t="s">
         <v>52</v>
       </c>
@@ -20379,7 +20374,7 @@
         <v>29110</v>
       </c>
     </row>
-    <row r="126" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A126" s="53" t="s">
         <v>67</v>
       </c>
@@ -20411,7 +20406,7 @@
         <v>39243</v>
       </c>
     </row>
-    <row r="127" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A127" s="50" t="s">
         <v>54</v>
       </c>
@@ -20443,7 +20438,7 @@
         <v>37.4</v>
       </c>
     </row>
-    <row r="128" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A128" s="50" t="s">
         <v>55</v>
       </c>
@@ -20475,7 +20470,7 @@
         <v>35.799999999999997</v>
       </c>
     </row>
-    <row r="129" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A129" s="1"/>
       <c r="B129" s="20"/>
       <c r="C129" s="20"/>
@@ -20487,7 +20482,7 @@
       <c r="I129" s="20"/>
       <c r="J129" s="20"/>
     </row>
-    <row r="130" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A130" s="48" t="s">
         <v>173</v>
       </c>
@@ -20501,7 +20496,7 @@
       <c r="I130" s="20"/>
       <c r="J130" s="20"/>
     </row>
-    <row r="131" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A131" s="50" t="s">
         <v>69</v>
       </c>
@@ -20533,7 +20528,7 @@
         <v>15.9</v>
       </c>
     </row>
-    <row r="132" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A132" s="50" t="s">
         <v>70</v>
       </c>
@@ -20565,7 +20560,7 @@
         <v>6.1</v>
       </c>
     </row>
-    <row r="133" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A133" s="1"/>
       <c r="B133" s="1"/>
       <c r="C133" s="1"/>
@@ -20577,7 +20572,7 @@
       <c r="I133" s="1"/>
       <c r="J133" s="1"/>
     </row>
-    <row r="134" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A134" s="73" t="s">
         <v>174</v>
       </c>
@@ -20591,7 +20586,7 @@
       <c r="I134" s="1"/>
       <c r="J134" s="1"/>
     </row>
-    <row r="135" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A135" s="50" t="s">
         <v>39</v>
       </c>
@@ -20623,7 +20618,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="136" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A136" s="50" t="s">
         <v>175</v>
       </c>
@@ -20655,7 +20650,7 @@
         <v>52637</v>
       </c>
     </row>
-    <row r="137" spans="1:10" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="137" s="6" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A137" s="57" t="s">
         <v>119</v>
       </c>
@@ -20687,7 +20682,7 @@
         <v>45550</v>
       </c>
     </row>
-    <row r="138" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A138" s="50" t="s">
         <v>41</v>
       </c>
@@ -20719,7 +20714,7 @@
         <v>1888</v>
       </c>
     </row>
-    <row r="139" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A139" s="18" t="s">
         <v>76</v>
       </c>
@@ -20751,7 +20746,7 @@
         <v>19412</v>
       </c>
     </row>
-    <row r="140" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A140" s="18" t="s">
         <v>148</v>
       </c>
@@ -20783,7 +20778,7 @@
         <v>4190</v>
       </c>
     </row>
-    <row r="141" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A141" s="18" t="s">
         <v>23</v>
       </c>
@@ -20815,7 +20810,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="142" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A142" s="18" t="s">
         <v>24</v>
       </c>
@@ -20847,7 +20842,7 @@
         <v>6703</v>
       </c>
     </row>
-    <row r="143" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A143" s="18" t="s">
         <v>78</v>
       </c>
@@ -20879,7 +20874,7 @@
         <v>33465</v>
       </c>
     </row>
-    <row r="144" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A144" s="18" t="s">
         <v>42</v>
       </c>
@@ -20911,7 +20906,7 @@
         <v>7638</v>
       </c>
     </row>
-    <row r="145" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A145" s="50" t="s">
         <v>43</v>
       </c>
@@ -20943,7 +20938,7 @@
         <v>31693</v>
       </c>
     </row>
-    <row r="146" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A146" s="18" t="s">
         <v>30</v>
       </c>
@@ -20975,7 +20970,7 @@
         <v>11709</v>
       </c>
     </row>
-    <row r="147" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A147" s="50" t="s">
         <v>31</v>
       </c>
@@ -21007,7 +21002,7 @@
         <v>12692</v>
       </c>
     </row>
-    <row r="148" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A148" s="50" t="s">
         <v>44</v>
       </c>
@@ -21039,7 +21034,7 @@
         <v>15904</v>
       </c>
     </row>
-    <row r="149" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A149" s="50" t="s">
         <v>176</v>
       </c>
@@ -21071,7 +21066,7 @@
         <v>164242</v>
       </c>
     </row>
-    <row r="150" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A150" s="54" t="s">
         <v>177</v>
       </c>
@@ -21103,7 +21098,7 @@
         <v>43889</v>
       </c>
     </row>
-    <row r="151" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A151" s="50" t="s">
         <v>35</v>
       </c>
@@ -21135,7 +21130,7 @@
         <v>8199</v>
       </c>
     </row>
-    <row r="152" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A152" s="50"/>
       <c r="B152" s="51"/>
       <c r="C152" s="51"/>
@@ -21147,7 +21142,7 @@
       <c r="I152" s="51"/>
       <c r="J152" s="51"/>
     </row>
-    <row r="153" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="153" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A153" s="48" t="s">
         <v>89</v>
       </c>
@@ -21161,7 +21156,7 @@
       <c r="I153" s="55"/>
       <c r="J153" s="55"/>
     </row>
-    <row r="154" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A154" s="24" t="s">
         <v>90</v>
       </c>
@@ -21193,7 +21188,7 @@
         <v>33615</v>
       </c>
     </row>
-    <row r="155" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A155" s="24" t="s">
         <v>91</v>
       </c>
@@ -21225,7 +21220,7 @@
         <v>7455</v>
       </c>
     </row>
-    <row r="156" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A156" s="24" t="s">
         <v>92</v>
       </c>
@@ -21257,7 +21252,7 @@
         <v>11094</v>
       </c>
     </row>
-    <row r="157" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A157" s="24" t="s">
         <v>93</v>
       </c>
@@ -21289,7 +21284,7 @@
         <v>10348</v>
       </c>
     </row>
-    <row r="158" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A158" s="24" t="s">
         <v>94</v>
       </c>
@@ -21321,7 +21316,7 @@
         <v>31748</v>
       </c>
     </row>
-    <row r="159" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A159" s="24" t="s">
         <v>178</v>
       </c>
@@ -21353,7 +21348,7 @@
         <v>236381</v>
       </c>
     </row>
-    <row r="160" spans="1:10" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="160" s="6" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A160" s="42" t="s">
         <v>179</v>
       </c>
@@ -21385,7 +21380,7 @@
         <v>233112</v>
       </c>
     </row>
-    <row r="161" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A161" s="24" t="s">
         <v>95</v>
       </c>
@@ -21417,7 +21412,7 @@
         <v>46880</v>
       </c>
     </row>
-    <row r="162" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A162" s="24" t="s">
         <v>96</v>
       </c>
@@ -21449,7 +21444,7 @@
         <v>37030</v>
       </c>
     </row>
-    <row r="163" spans="1:10" ht="25.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="163" ht="25.65" customHeight="1" ns3:dyDescent="0.3">
       <c r="A163" s="26" t="s">
         <v>202</v>
       </c>
@@ -21481,7 +21476,7 @@
         <v>414586</v>
       </c>
     </row>
-    <row r="164" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="164" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A164" s="47"/>
       <c r="B164" s="110" t="s">
         <v>99</v>
@@ -21495,7 +21490,7 @@
       <c r="I164" s="110"/>
       <c r="J164" s="110"/>
     </row>
-    <row r="165" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A165" s="48" t="s">
         <v>64</v>
       </c>
@@ -21509,7 +21504,7 @@
       <c r="I165" s="49"/>
       <c r="J165" s="49"/>
     </row>
-    <row r="166" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A166" s="50" t="s">
         <v>38</v>
       </c>
@@ -21541,7 +21536,7 @@
         <v>14614</v>
       </c>
     </row>
-    <row r="167" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A167" s="50" t="s">
         <v>45</v>
       </c>
@@ -21573,7 +21568,7 @@
         <v>5043</v>
       </c>
     </row>
-    <row r="168" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A168" s="50"/>
       <c r="B168" s="51"/>
       <c r="C168" s="51"/>
@@ -21585,7 +21580,7 @@
       <c r="I168" s="51"/>
       <c r="J168" s="51"/>
     </row>
-    <row r="169" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A169" s="52" t="s">
         <v>53</v>
       </c>
@@ -21599,7 +21594,7 @@
       <c r="I169" s="51"/>
       <c r="J169" s="51"/>
     </row>
-    <row r="170" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A170" s="53" t="s">
         <v>100</v>
       </c>
@@ -21631,7 +21626,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="171" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A171" s="53" t="s">
         <v>101</v>
       </c>
@@ -21663,7 +21658,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="172" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A172" s="53" t="s">
         <v>102</v>
       </c>
@@ -21695,7 +21690,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="173" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A173" s="53" t="s">
         <v>103</v>
       </c>
@@ -21727,7 +21722,7 @@
         <v>942</v>
       </c>
     </row>
-    <row r="174" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A174" s="53" t="s">
         <v>104</v>
       </c>
@@ -21759,7 +21754,7 @@
         <v>2261</v>
       </c>
     </row>
-    <row r="175" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A175" s="53" t="s">
         <v>105</v>
       </c>
@@ -21791,7 +21786,7 @@
         <v>3875</v>
       </c>
     </row>
-    <row r="176" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A176" s="53" t="s">
         <v>106</v>
       </c>
@@ -21823,7 +21818,7 @@
         <v>4454</v>
       </c>
     </row>
-    <row r="177" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A177" s="53" t="s">
         <v>107</v>
       </c>
@@ -21855,7 +21850,7 @@
         <v>5182</v>
       </c>
     </row>
-    <row r="178" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A178" s="53" t="s">
         <v>108</v>
       </c>
@@ -21887,7 +21882,7 @@
         <v>2222</v>
       </c>
     </row>
-    <row r="179" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A179" s="53" t="s">
         <v>109</v>
       </c>
@@ -21919,7 +21914,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="180" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A180" s="53" t="s">
         <v>46</v>
       </c>
@@ -21951,7 +21946,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="181" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A181" s="53" t="s">
         <v>110</v>
       </c>
@@ -21983,7 +21978,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="182" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A182" s="50" t="s">
         <v>54</v>
       </c>
@@ -22015,7 +22010,7 @@
         <v>16.399999999999999</v>
       </c>
     </row>
-    <row r="183" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A183" s="50" t="s">
         <v>55</v>
       </c>
@@ -22047,7 +22042,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="184" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A184" s="1"/>
       <c r="B184" s="20"/>
       <c r="C184" s="20"/>
@@ -22059,7 +22054,7 @@
       <c r="I184" s="20"/>
       <c r="J184" s="20"/>
     </row>
-    <row r="185" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A185" s="48" t="s">
         <v>173</v>
       </c>
@@ -22073,7 +22068,7 @@
       <c r="I185" s="20"/>
       <c r="J185" s="20"/>
     </row>
-    <row r="186" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A186" s="50" t="s">
         <v>69</v>
       </c>
@@ -22105,7 +22100,7 @@
         <v>16.399999999999999</v>
       </c>
     </row>
-    <row r="187" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A187" s="50" t="s">
         <v>70</v>
       </c>
@@ -22137,7 +22132,7 @@
         <v>9.3000000000000007</v>
       </c>
     </row>
-    <row r="188" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A188" s="1"/>
       <c r="B188" s="1"/>
       <c r="C188" s="1"/>
@@ -22149,7 +22144,7 @@
       <c r="I188" s="1"/>
       <c r="J188" s="1"/>
     </row>
-    <row r="189" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A189" s="73" t="s">
         <v>174</v>
       </c>
@@ -22163,7 +22158,7 @@
       <c r="I189" s="1"/>
       <c r="J189" s="1"/>
     </row>
-    <row r="190" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A190" s="50" t="s">
         <v>39</v>
       </c>
@@ -22195,7 +22190,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="191" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A191" s="50" t="s">
         <v>175</v>
       </c>
@@ -22227,7 +22222,7 @@
         <v>4739</v>
       </c>
     </row>
-    <row r="192" spans="1:10" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="192" s="6" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A192" s="57" t="s">
         <v>119</v>
       </c>
@@ -22259,7 +22254,7 @@
         <v>4314</v>
       </c>
     </row>
-    <row r="193" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A193" s="50" t="s">
         <v>41</v>
       </c>
@@ -22291,7 +22286,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="194" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A194" s="18" t="s">
         <v>76</v>
       </c>
@@ -22323,7 +22318,7 @@
         <v>985</v>
       </c>
     </row>
-    <row r="195" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A195" s="18" t="s">
         <v>148</v>
       </c>
@@ -22355,7 +22350,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="196" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A196" s="18" t="s">
         <v>23</v>
       </c>
@@ -22387,7 +22382,7 @@
         <v>1331</v>
       </c>
     </row>
-    <row r="197" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A197" s="18" t="s">
         <v>24</v>
       </c>
@@ -22419,7 +22414,7 @@
         <v>2940</v>
       </c>
     </row>
-    <row r="198" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A198" s="18" t="s">
         <v>78</v>
       </c>
@@ -22451,7 +22446,7 @@
         <v>4069</v>
       </c>
     </row>
-    <row r="199" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A199" s="18" t="s">
         <v>42</v>
       </c>
@@ -22483,7 +22478,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="200" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A200" s="50" t="s">
         <v>43</v>
       </c>
@@ -22515,7 +22510,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="201" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A201" s="18" t="s">
         <v>30</v>
       </c>
@@ -22547,7 +22542,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="202" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A202" s="50" t="s">
         <v>31</v>
       </c>
@@ -22579,7 +22574,7 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="203" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A203" s="50" t="s">
         <v>44</v>
       </c>
@@ -22611,7 +22606,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="204" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A204" s="50" t="s">
         <v>176</v>
       </c>
@@ -22643,7 +22638,7 @@
         <v>1233</v>
       </c>
     </row>
-    <row r="205" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A205" s="54" t="s">
         <v>177</v>
       </c>
@@ -22675,7 +22670,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="206" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A206" s="50" t="s">
         <v>35</v>
       </c>
@@ -22707,7 +22702,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="207" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A207" s="50"/>
       <c r="B207" s="1"/>
       <c r="C207" s="1"/>
@@ -22719,7 +22714,7 @@
       <c r="I207" s="1"/>
       <c r="J207" s="1"/>
     </row>
-    <row r="208" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="208" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A208" s="48" t="s">
         <v>89</v>
       </c>
@@ -22733,7 +22728,7 @@
       <c r="I208" s="55"/>
       <c r="J208" s="55"/>
     </row>
-    <row r="209" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A209" s="24" t="s">
         <v>90</v>
       </c>
@@ -22765,7 +22760,7 @@
         <v>1116</v>
       </c>
     </row>
-    <row r="210" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A210" s="24" t="s">
         <v>91</v>
       </c>
@@ -22797,7 +22792,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="211" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A211" s="24" t="s">
         <v>92</v>
       </c>
@@ -22829,7 +22824,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="212" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A212" s="24" t="s">
         <v>93</v>
       </c>
@@ -22861,7 +22856,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="213" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A213" s="24" t="s">
         <v>94</v>
       </c>
@@ -22893,7 +22888,7 @@
         <v>3569</v>
       </c>
     </row>
-    <row r="214" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A214" s="24" t="s">
         <v>178</v>
       </c>
@@ -22925,7 +22920,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="215" spans="1:10" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="215" s="6" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A215" s="42" t="s">
         <v>179</v>
       </c>
@@ -22957,7 +22952,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="216" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A216" s="24" t="s">
         <v>95</v>
       </c>
@@ -22989,7 +22984,7 @@
         <v>2925</v>
       </c>
     </row>
-    <row r="217" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A217" s="24" t="s">
         <v>96</v>
       </c>
@@ -23021,7 +23016,7 @@
         <v>9726</v>
       </c>
     </row>
-    <row r="218" spans="1:10" s="81" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="218" s="81" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A218" s="41" t="s">
         <v>182</v>
       </c>
@@ -23053,7 +23048,7 @@
         <v>4523</v>
       </c>
     </row>
-    <row r="219" spans="1:10" ht="25.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="219" ht="25.65" customHeight="1" ns3:dyDescent="0.3">
       <c r="A219" s="26" t="s">
         <v>202</v>
       </c>
@@ -23085,7 +23080,7 @@
         <v>19775</v>
       </c>
     </row>
-    <row r="220" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="220" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A220" s="26"/>
       <c r="B220" s="28"/>
       <c r="C220" s="28"/>
@@ -23097,47 +23092,47 @@
       <c r="I220" s="28"/>
       <c r="J220" s="28"/>
     </row>
-    <row r="221" spans="1:10" s="112" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" s="112" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A221" s="112" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="222" spans="1:10" s="112" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" s="112" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A222" s="112" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="223" spans="1:10" s="111" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" s="111" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A223" s="111" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="224" spans="1:10" s="111" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" s="111" customFormat="1" ht="30" customHeight="1" ns3:dyDescent="0.25">
       <c r="A224" s="111" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="225" spans="1:10" s="111" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" s="111" customFormat="1" ht="30" customHeight="1" ns3:dyDescent="0.25">
       <c r="A225" s="111" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="226" spans="1:10" s="114" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" s="114" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A226" s="114" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="227" spans="1:10" s="111" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" s="111" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A227" s="111" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="228" spans="1:10" s="111" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" s="111" customFormat="1" ht="30" customHeight="1" ns3:dyDescent="0.25">
       <c r="A228" s="111" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="229" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" ht="45" customHeight="1" ns3:dyDescent="0.25">
       <c r="A229" s="111" t="s">
         <v>216</v>
       </c>
@@ -23151,58 +23146,44 @@
       <c r="I229" s="111"/>
       <c r="J229" s="111"/>
     </row>
-    <row r="230" spans="1:10" s="112" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" s="112" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A230" s="112" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="231" spans="1:10" s="111" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" s="111" customFormat="1" ht="30" customHeight="1" ns3:dyDescent="0.25">
       <c r="A231" s="111" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="232" spans="1:10" s="111" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" s="111" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A232" s="111" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="233" spans="1:10" s="115" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" s="115" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A233" s="115" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="234" spans="1:10" s="107" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" s="107" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A234" s="107" t="s">
         <v>9</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1"/>
-  <mergeCells count="21">
-    <mergeCell ref="A227:XFD227"/>
-    <mergeCell ref="A228:XFD228"/>
-    <mergeCell ref="A230:XFD230"/>
-    <mergeCell ref="A231:XFD231"/>
-    <mergeCell ref="A232:XFD232"/>
-    <mergeCell ref="A234:XFD234"/>
+  <mergeCells count="7">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="B5:J5"/>
     <mergeCell ref="B58:J58"/>
     <mergeCell ref="B111:J111"/>
     <mergeCell ref="B164:J164"/>
     <mergeCell ref="A229:J229"/>
-    <mergeCell ref="A221:XFD221"/>
-    <mergeCell ref="A222:XFD222"/>
-    <mergeCell ref="A223:XFD223"/>
-    <mergeCell ref="A224:XFD224"/>
-    <mergeCell ref="A2:O2"/>
     <mergeCell ref="A3:J3"/>
-    <mergeCell ref="A225:XFD225"/>
-    <mergeCell ref="A226:XFD226"/>
-    <mergeCell ref="A233:XFD233"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A234" r:id="rId1" location="copyright-and-creative-commons" xr:uid="{C26E78A9-2BD0-4502-B496-9C5E482783E4}"/>
+    <hyperlink ref="A234" r:id="rId1" location="copyright-and-creative-commons" ns2:uid="{C26E78A9-2BD0-4502-B496-9C5E482783E4}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
@@ -23211,12 +23192,12 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97DC0960-392B-4EA9-A2F7-722BE53943E0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{97DC0960-392B-4EA9-A2F7-722BE53943E0}">
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
   <dimension ref="A1:S150"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" customHeight="1" zeroHeight="1" ns3:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.6328125" style="1" customWidth="1"/>
     <col min="2" max="3" width="16.453125" style="15" customWidth="1"/>
@@ -23233,10 +23214,9 @@
     <col min="16" max="16" width="11.453125" style="15" customWidth="1"/>
     <col min="17" max="17" width="14.453125" style="15" customWidth="1"/>
     <col min="18" max="19" width="11.453125" style="15" customWidth="1"/>
-    <col min="20" max="16384" width="0" style="1" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="73" customFormat="1" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" s="73" customFormat="1" ht="5.0999999999999996" customHeight="1" ns3:dyDescent="0.25">
       <c r="A1" s="105" t="s">
         <v>233</v>
       </c>
@@ -23259,7 +23239,7 @@
       <c r="R1" s="105"/>
       <c r="S1" s="105"/>
     </row>
-    <row r="2" spans="1:19" s="86" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" s="86" customFormat="1" ht="60" customHeight="1" ns3:dyDescent="0.25">
       <c r="A2" s="96" t="s">
         <v>1</v>
       </c>
@@ -23282,7 +23262,7 @@
       <c r="R2" s="96"/>
       <c r="S2" s="96"/>
     </row>
-    <row r="3" spans="1:19" customFormat="1" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="3" customFormat="1" ht="36" customHeight="1" thickBot="1" ns3:dyDescent="0.45">
       <c r="A3" s="113" t="s">
         <v>125</v>
       </c>
@@ -23305,7 +23285,7 @@
       <c r="R3" s="113"/>
       <c r="S3" s="113"/>
     </row>
-    <row r="4" spans="1:19" s="12" customFormat="1" ht="64.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="4" s="12" customFormat="1" ht="64.5" customHeight="1" thickTop="1" ns3:dyDescent="0.3">
       <c r="A4" s="118" t="s">
         <v>130</v>
       </c>
@@ -23364,7 +23344,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="5" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A5" s="118"/>
       <c r="B5" s="117" t="s">
         <v>37</v>
@@ -23389,7 +23369,7 @@
       <c r="R5" s="117"/>
       <c r="S5" s="117"/>
     </row>
-    <row r="6" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A6" s="60"/>
       <c r="B6" s="116" t="s">
         <v>63</v>
@@ -23412,7 +23392,7 @@
       <c r="R6" s="116"/>
       <c r="S6" s="116"/>
     </row>
-    <row r="7" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A7" s="61" t="s">
         <v>38</v>
       </c>
@@ -23435,7 +23415,7 @@
       <c r="R7" s="4"/>
       <c r="S7" s="4"/>
     </row>
-    <row r="8" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A8" s="62" t="s">
         <v>66</v>
       </c>
@@ -23494,7 +23474,7 @@
         <v>29039</v>
       </c>
     </row>
-    <row r="9" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A9" s="62" t="s">
         <v>46</v>
       </c>
@@ -23553,7 +23533,7 @@
         <v>43703</v>
       </c>
     </row>
-    <row r="10" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A10" s="62" t="s">
         <v>47</v>
       </c>
@@ -23612,7 +23592,7 @@
         <v>45573</v>
       </c>
     </row>
-    <row r="11" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A11" s="62" t="s">
         <v>48</v>
       </c>
@@ -23671,7 +23651,7 @@
         <v>46575</v>
       </c>
     </row>
-    <row r="12" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A12" s="62" t="s">
         <v>49</v>
       </c>
@@ -23730,7 +23710,7 @@
         <v>43310</v>
       </c>
     </row>
-    <row r="13" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A13" s="62" t="s">
         <v>50</v>
       </c>
@@ -23789,7 +23769,7 @@
         <v>39337</v>
       </c>
     </row>
-    <row r="14" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A14" s="62" t="s">
         <v>51</v>
       </c>
@@ -23848,7 +23828,7 @@
         <v>29541</v>
       </c>
     </row>
-    <row r="15" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A15" s="62" t="s">
         <v>52</v>
       </c>
@@ -23907,7 +23887,7 @@
         <v>22928</v>
       </c>
     </row>
-    <row r="16" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A16" s="62" t="s">
         <v>67</v>
       </c>
@@ -23966,7 +23946,7 @@
         <v>32368</v>
       </c>
     </row>
-    <row r="17" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A17" s="63" t="s">
         <v>146</v>
       </c>
@@ -24025,7 +24005,7 @@
         <v>334190</v>
       </c>
     </row>
-    <row r="18" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A18" s="63"/>
       <c r="B18" s="15"/>
       <c r="C18" s="15"/>
@@ -24046,7 +24026,7 @@
       <c r="R18" s="15"/>
       <c r="S18" s="15"/>
     </row>
-    <row r="19" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A19" s="64" t="s">
         <v>45</v>
       </c>
@@ -24069,7 +24049,7 @@
       <c r="R19" s="15"/>
       <c r="S19" s="15"/>
     </row>
-    <row r="20" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A20" s="62" t="s">
         <v>66</v>
       </c>
@@ -24128,7 +24108,7 @@
         <v>9228</v>
       </c>
     </row>
-    <row r="21" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A21" s="62" t="s">
         <v>46</v>
       </c>
@@ -24187,7 +24167,7 @@
         <v>13924</v>
       </c>
     </row>
-    <row r="22" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A22" s="62" t="s">
         <v>47</v>
       </c>
@@ -24246,7 +24226,7 @@
         <v>15054</v>
       </c>
     </row>
-    <row r="23" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A23" s="62" t="s">
         <v>48</v>
       </c>
@@ -24305,7 +24285,7 @@
         <v>15913</v>
       </c>
     </row>
-    <row r="24" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A24" s="62" t="s">
         <v>49</v>
       </c>
@@ -24364,7 +24344,7 @@
         <v>14932</v>
       </c>
     </row>
-    <row r="25" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A25" s="62" t="s">
         <v>50</v>
       </c>
@@ -24423,7 +24403,7 @@
         <v>12876</v>
       </c>
     </row>
-    <row r="26" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A26" s="62" t="s">
         <v>51</v>
       </c>
@@ -24482,7 +24462,7 @@
         <v>9375</v>
       </c>
     </row>
-    <row r="27" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A27" s="62" t="s">
         <v>52</v>
       </c>
@@ -24541,7 +24521,7 @@
         <v>6795</v>
       </c>
     </row>
-    <row r="28" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A28" s="62" t="s">
         <v>67</v>
       </c>
@@ -24600,7 +24580,7 @@
         <v>7846</v>
       </c>
     </row>
-    <row r="29" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A29" s="63" t="s">
         <v>146</v>
       </c>
@@ -24659,7 +24639,7 @@
         <v>107125</v>
       </c>
     </row>
-    <row r="30" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A30" s="63"/>
       <c r="B30" s="15"/>
       <c r="C30" s="15"/>
@@ -24680,7 +24660,7 @@
       <c r="R30" s="15"/>
       <c r="S30" s="15"/>
     </row>
-    <row r="31" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A31" s="61" t="s">
         <v>158</v>
       </c>
@@ -24703,7 +24683,7 @@
       <c r="R31" s="15"/>
       <c r="S31" s="15"/>
     </row>
-    <row r="32" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A32" s="62" t="s">
         <v>66</v>
       </c>
@@ -24762,7 +24742,7 @@
         <v>38460</v>
       </c>
     </row>
-    <row r="33" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A33" s="62" t="s">
         <v>46</v>
       </c>
@@ -24821,7 +24801,7 @@
         <v>57805</v>
       </c>
     </row>
-    <row r="34" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A34" s="62" t="s">
         <v>47</v>
       </c>
@@ -24880,7 +24860,7 @@
         <v>60810</v>
       </c>
     </row>
-    <row r="35" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A35" s="62" t="s">
         <v>48</v>
       </c>
@@ -24939,7 +24919,7 @@
         <v>62660</v>
       </c>
     </row>
-    <row r="36" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A36" s="62" t="s">
         <v>49</v>
       </c>
@@ -24998,7 +24978,7 @@
         <v>58408</v>
       </c>
     </row>
-    <row r="37" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A37" s="62" t="s">
         <v>50</v>
       </c>
@@ -25057,7 +25037,7 @@
         <v>52363</v>
       </c>
     </row>
-    <row r="38" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A38" s="62" t="s">
         <v>51</v>
       </c>
@@ -25116,7 +25096,7 @@
         <v>39022</v>
       </c>
     </row>
-    <row r="39" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A39" s="62" t="s">
         <v>52</v>
       </c>
@@ -25175,7 +25155,7 @@
         <v>29839</v>
       </c>
     </row>
-    <row r="40" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A40" s="62" t="s">
         <v>67</v>
       </c>
@@ -25234,7 +25214,7 @@
         <v>40396</v>
       </c>
     </row>
-    <row r="41" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A41" s="63" t="s">
         <v>146</v>
       </c>
@@ -25293,7 +25273,7 @@
         <v>442922</v>
       </c>
     </row>
-    <row r="42" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A42" s="63"/>
       <c r="B42" s="15"/>
       <c r="C42" s="15"/>
@@ -25314,7 +25294,7 @@
       <c r="R42" s="15"/>
       <c r="S42" s="15"/>
     </row>
-    <row r="43" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A43" s="64" t="s">
         <v>65</v>
       </c>
@@ -25373,7 +25353,7 @@
         <v>4200</v>
       </c>
     </row>
-    <row r="44" spans="1:19" s="12" customFormat="1" ht="25.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" s="12" customFormat="1" ht="25.65" customHeight="1" ns3:dyDescent="0.3">
       <c r="A44" s="66" t="s">
         <v>132</v>
       </c>
@@ -25432,7 +25412,7 @@
         <v>447122</v>
       </c>
     </row>
-    <row r="45" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A45" s="60"/>
       <c r="B45" s="116" t="s">
         <v>97</v>
@@ -25455,7 +25435,7 @@
       <c r="R45" s="116"/>
       <c r="S45" s="116"/>
     </row>
-    <row r="46" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A46" s="61" t="s">
         <v>38</v>
       </c>
@@ -25478,7 +25458,7 @@
       <c r="R46" s="4"/>
       <c r="S46" s="4"/>
     </row>
-    <row r="47" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A47" s="62" t="s">
         <v>66</v>
       </c>
@@ -25537,7 +25517,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="48" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A48" s="62" t="s">
         <v>46</v>
       </c>
@@ -25596,7 +25576,7 @@
         <v>1633</v>
       </c>
     </row>
-    <row r="49" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A49" s="62" t="s">
         <v>47</v>
       </c>
@@ -25655,7 +25635,7 @@
         <v>1758</v>
       </c>
     </row>
-    <row r="50" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A50" s="62" t="s">
         <v>48</v>
       </c>
@@ -25714,7 +25694,7 @@
         <v>1903</v>
       </c>
     </row>
-    <row r="51" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A51" s="62" t="s">
         <v>49</v>
       </c>
@@ -25773,7 +25753,7 @@
         <v>1570</v>
       </c>
     </row>
-    <row r="52" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A52" s="62" t="s">
         <v>50</v>
       </c>
@@ -25832,7 +25812,7 @@
         <v>1277</v>
       </c>
     </row>
-    <row r="53" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A53" s="62" t="s">
         <v>51</v>
       </c>
@@ -25891,7 +25871,7 @@
         <v>897</v>
       </c>
     </row>
-    <row r="54" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A54" s="62" t="s">
         <v>52</v>
       </c>
@@ -25950,7 +25930,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="55" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A55" s="62" t="s">
         <v>67</v>
       </c>
@@ -26009,7 +25989,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="56" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A56" s="63" t="s">
         <v>146</v>
       </c>
@@ -26068,7 +26048,7 @@
         <v>11035</v>
       </c>
     </row>
-    <row r="57" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A57" s="63"/>
       <c r="B57" s="15"/>
       <c r="C57" s="15"/>
@@ -26089,7 +26069,7 @@
       <c r="R57" s="15"/>
       <c r="S57" s="15"/>
     </row>
-    <row r="58" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A58" s="64" t="s">
         <v>45</v>
       </c>
@@ -26112,7 +26092,7 @@
       <c r="R58" s="15"/>
       <c r="S58" s="15"/>
     </row>
-    <row r="59" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A59" s="62" t="s">
         <v>66</v>
       </c>
@@ -26171,7 +26151,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="60" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A60" s="62" t="s">
         <v>46</v>
       </c>
@@ -26230,7 +26210,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="61" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A61" s="62" t="s">
         <v>47</v>
       </c>
@@ -26289,7 +26269,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="62" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A62" s="62" t="s">
         <v>48</v>
       </c>
@@ -26348,7 +26328,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="63" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A63" s="62" t="s">
         <v>49</v>
       </c>
@@ -26407,7 +26387,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="64" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A64" s="62" t="s">
         <v>50</v>
       </c>
@@ -26466,7 +26446,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="65" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A65" s="62" t="s">
         <v>51</v>
       </c>
@@ -26525,7 +26505,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="66" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A66" s="62" t="s">
         <v>52</v>
       </c>
@@ -26584,7 +26564,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="67" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A67" s="62" t="s">
         <v>67</v>
       </c>
@@ -26643,7 +26623,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="68" spans="1:19" s="70" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" s="70" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A68" s="63" t="s">
         <v>146</v>
       </c>
@@ -26702,7 +26682,7 @@
         <v>1660</v>
       </c>
     </row>
-    <row r="69" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A69" s="63"/>
       <c r="B69" s="15"/>
       <c r="C69" s="15"/>
@@ -26723,7 +26703,7 @@
       <c r="R69" s="15"/>
       <c r="S69" s="15"/>
     </row>
-    <row r="70" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A70" s="61" t="s">
         <v>158</v>
       </c>
@@ -26746,7 +26726,7 @@
       <c r="R70" s="15"/>
       <c r="S70" s="15"/>
     </row>
-    <row r="71" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A71" s="62" t="s">
         <v>66</v>
       </c>
@@ -26805,7 +26785,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="72" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A72" s="62" t="s">
         <v>46</v>
       </c>
@@ -26864,7 +26844,7 @@
         <v>1848</v>
       </c>
     </row>
-    <row r="73" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A73" s="62" t="s">
         <v>47</v>
       </c>
@@ -26923,7 +26903,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="74" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A74" s="62" t="s">
         <v>48</v>
       </c>
@@ -26982,7 +26962,7 @@
         <v>2177</v>
       </c>
     </row>
-    <row r="75" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A75" s="62" t="s">
         <v>49</v>
       </c>
@@ -27041,7 +27021,7 @@
         <v>1854</v>
       </c>
     </row>
-    <row r="76" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A76" s="62" t="s">
         <v>50</v>
       </c>
@@ -27100,7 +27080,7 @@
         <v>1493</v>
       </c>
     </row>
-    <row r="77" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A77" s="62" t="s">
         <v>51</v>
       </c>
@@ -27159,7 +27139,7 @@
         <v>1015</v>
       </c>
     </row>
-    <row r="78" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A78" s="62" t="s">
         <v>52</v>
       </c>
@@ -27218,7 +27198,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="79" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A79" s="62" t="s">
         <v>67</v>
       </c>
@@ -27277,7 +27257,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="80" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A80" s="63" t="s">
         <v>146</v>
       </c>
@@ -27336,8 +27316,8 @@
         <v>12703</v>
       </c>
     </row>
-    <row r="81" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="82" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" ht="15" customHeight="1" ns3:dyDescent="0.25"/>
+    <row r="82" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A82" s="64" t="s">
         <v>65</v>
       </c>
@@ -27396,7 +27376,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="83" spans="1:19" s="12" customFormat="1" ht="25.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" s="12" customFormat="1" ht="25.65" customHeight="1" ns3:dyDescent="0.3">
       <c r="A83" s="66" t="s">
         <v>132</v>
       </c>
@@ -27455,7 +27435,7 @@
         <v>12763</v>
       </c>
     </row>
-    <row r="84" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A84" s="60"/>
       <c r="B84" s="116" t="s">
         <v>98</v>
@@ -27478,7 +27458,7 @@
       <c r="R84" s="116"/>
       <c r="S84" s="116"/>
     </row>
-    <row r="85" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A85" s="61" t="s">
         <v>38</v>
       </c>
@@ -27501,7 +27481,7 @@
       <c r="R85" s="4"/>
       <c r="S85" s="4"/>
     </row>
-    <row r="86" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A86" s="62" t="s">
         <v>66</v>
       </c>
@@ -27560,7 +27540,7 @@
         <v>14208</v>
       </c>
     </row>
-    <row r="87" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A87" s="62" t="s">
         <v>46</v>
       </c>
@@ -27619,7 +27599,7 @@
         <v>41961</v>
       </c>
     </row>
-    <row r="88" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A88" s="62" t="s">
         <v>47</v>
       </c>
@@ -27678,7 +27658,7 @@
         <v>43810</v>
       </c>
     </row>
-    <row r="89" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A89" s="62" t="s">
         <v>48</v>
       </c>
@@ -27737,7 +27717,7 @@
         <v>44670</v>
       </c>
     </row>
-    <row r="90" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A90" s="62" t="s">
         <v>49</v>
       </c>
@@ -27796,7 +27776,7 @@
         <v>41741</v>
       </c>
     </row>
-    <row r="91" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A91" s="62" t="s">
         <v>50</v>
       </c>
@@ -27855,7 +27835,7 @@
         <v>38057</v>
       </c>
     </row>
-    <row r="92" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A92" s="62" t="s">
         <v>51</v>
       </c>
@@ -27914,7 +27894,7 @@
         <v>28648</v>
       </c>
     </row>
-    <row r="93" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A93" s="62" t="s">
         <v>52</v>
       </c>
@@ -27973,7 +27953,7 @@
         <v>22326</v>
       </c>
     </row>
-    <row r="94" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A94" s="62" t="s">
         <v>67</v>
       </c>
@@ -28032,7 +28012,7 @@
         <v>31317</v>
       </c>
     </row>
-    <row r="95" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A95" s="63" t="s">
         <v>146</v>
       </c>
@@ -28091,8 +28071,8 @@
         <v>308532</v>
       </c>
     </row>
-    <row r="96" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="97" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" ht="15" customHeight="1" ns3:dyDescent="0.25"/>
+    <row r="97" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A97" s="64" t="s">
         <v>45</v>
       </c>
@@ -28115,7 +28095,7 @@
       <c r="R97" s="15"/>
       <c r="S97" s="15"/>
     </row>
-    <row r="98" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A98" s="62" t="s">
         <v>66</v>
       </c>
@@ -28174,7 +28154,7 @@
         <v>4160</v>
       </c>
     </row>
-    <row r="99" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A99" s="62" t="s">
         <v>46</v>
       </c>
@@ -28233,7 +28213,7 @@
         <v>13682</v>
       </c>
     </row>
-    <row r="100" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A100" s="62" t="s">
         <v>47</v>
       </c>
@@ -28292,7 +28272,7 @@
         <v>14791</v>
       </c>
     </row>
-    <row r="101" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A101" s="62" t="s">
         <v>48</v>
       </c>
@@ -28351,7 +28331,7 @@
         <v>15640</v>
       </c>
     </row>
-    <row r="102" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A102" s="62" t="s">
         <v>49</v>
       </c>
@@ -28410,7 +28390,7 @@
         <v>14646</v>
       </c>
     </row>
-    <row r="103" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A103" s="62" t="s">
         <v>50</v>
       </c>
@@ -28469,7 +28449,7 @@
         <v>12666</v>
       </c>
     </row>
-    <row r="104" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A104" s="62" t="s">
         <v>51</v>
       </c>
@@ -28528,7 +28508,7 @@
         <v>9254</v>
       </c>
     </row>
-    <row r="105" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A105" s="62" t="s">
         <v>52</v>
       </c>
@@ -28587,7 +28567,7 @@
         <v>6673</v>
       </c>
     </row>
-    <row r="106" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A106" s="62" t="s">
         <v>67</v>
       </c>
@@ -28646,7 +28626,7 @@
         <v>7739</v>
       </c>
     </row>
-    <row r="107" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A107" s="63" t="s">
         <v>146</v>
       </c>
@@ -28705,7 +28685,7 @@
         <v>100425</v>
       </c>
     </row>
-    <row r="108" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A108" s="63"/>
       <c r="B108" s="15"/>
       <c r="C108" s="15"/>
@@ -28726,7 +28706,7 @@
       <c r="R108" s="15"/>
       <c r="S108" s="15"/>
     </row>
-    <row r="109" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A109" s="61" t="s">
         <v>158</v>
       </c>
@@ -28749,7 +28729,7 @@
       <c r="R109" s="15"/>
       <c r="S109" s="15"/>
     </row>
-    <row r="110" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A110" s="62" t="s">
         <v>66</v>
       </c>
@@ -28808,7 +28788,7 @@
         <v>18428</v>
       </c>
     </row>
-    <row r="111" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A111" s="62" t="s">
         <v>46</v>
       </c>
@@ -28867,7 +28847,7 @@
         <v>55820</v>
       </c>
     </row>
-    <row r="112" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A112" s="62" t="s">
         <v>47</v>
       </c>
@@ -28926,7 +28906,7 @@
         <v>58781</v>
       </c>
     </row>
-    <row r="113" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A113" s="62" t="s">
         <v>48</v>
       </c>
@@ -28985,7 +28965,7 @@
         <v>60478</v>
       </c>
     </row>
-    <row r="114" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A114" s="62" t="s">
         <v>49</v>
       </c>
@@ -29044,7 +29024,7 @@
         <v>56546</v>
       </c>
     </row>
-    <row r="115" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A115" s="62" t="s">
         <v>50</v>
       </c>
@@ -29103,7 +29083,7 @@
         <v>50871</v>
       </c>
     </row>
-    <row r="116" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A116" s="62" t="s">
         <v>51</v>
       </c>
@@ -29162,7 +29142,7 @@
         <v>38002</v>
       </c>
     </row>
-    <row r="117" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="117" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A117" s="62" t="s">
         <v>52</v>
       </c>
@@ -29221,7 +29201,7 @@
         <v>29110</v>
       </c>
     </row>
-    <row r="118" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="118" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A118" s="62" t="s">
         <v>67</v>
       </c>
@@ -29280,7 +29260,7 @@
         <v>39243</v>
       </c>
     </row>
-    <row r="119" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="119" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A119" s="63" t="s">
         <v>146</v>
       </c>
@@ -29339,7 +29319,7 @@
         <v>410436</v>
       </c>
     </row>
-    <row r="120" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A120" s="63"/>
       <c r="B120" s="15"/>
       <c r="C120" s="15"/>
@@ -29360,7 +29340,7 @@
       <c r="R120" s="15"/>
       <c r="S120" s="15"/>
     </row>
-    <row r="121" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="121" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A121" s="64" t="s">
         <v>65</v>
       </c>
@@ -29419,7 +29399,7 @@
         <v>4144</v>
       </c>
     </row>
-    <row r="122" spans="1:19" s="12" customFormat="1" ht="25.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" s="12" customFormat="1" ht="25.65" customHeight="1" ns3:dyDescent="0.3">
       <c r="A122" s="66" t="s">
         <v>132</v>
       </c>
@@ -29478,7 +29458,7 @@
         <v>414586</v>
       </c>
     </row>
-    <row r="123" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="123" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A123" s="60"/>
       <c r="B123" s="116" t="s">
         <v>99</v>
@@ -29501,7 +29481,7 @@
       <c r="R123" s="116"/>
       <c r="S123" s="116"/>
     </row>
-    <row r="124" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="124" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A124" s="61" t="s">
         <v>38</v>
       </c>
@@ -29524,7 +29504,7 @@
       <c r="R124" s="4"/>
       <c r="S124" s="4"/>
     </row>
-    <row r="125" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="125" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A125" s="53" t="s">
         <v>136</v>
       </c>
@@ -29583,7 +29563,7 @@
         <v>2424</v>
       </c>
     </row>
-    <row r="126" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="126" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A126" s="53" t="s">
         <v>137</v>
       </c>
@@ -29642,7 +29622,7 @@
         <v>12061</v>
       </c>
     </row>
-    <row r="127" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="127" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A127" s="53" t="s">
         <v>46</v>
       </c>
@@ -29701,7 +29681,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="128" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="128" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A128" s="53" t="s">
         <v>110</v>
       </c>
@@ -29760,7 +29740,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="129" spans="1:19" s="70" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="129" s="70" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A129" s="63" t="s">
         <v>146</v>
       </c>
@@ -29819,7 +29799,7 @@
         <v>14614</v>
       </c>
     </row>
-    <row r="130" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="130" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A130" s="65"/>
       <c r="B130" s="15"/>
       <c r="C130" s="15"/>
@@ -29840,7 +29820,7 @@
       <c r="R130" s="15"/>
       <c r="S130" s="15"/>
     </row>
-    <row r="131" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="131" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A131" s="61" t="s">
         <v>45</v>
       </c>
@@ -29863,7 +29843,7 @@
       <c r="R131" s="15"/>
       <c r="S131" s="15"/>
     </row>
-    <row r="132" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="132" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A132" s="53" t="s">
         <v>136</v>
       </c>
@@ -29922,7 +29902,7 @@
         <v>1139</v>
       </c>
     </row>
-    <row r="133" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="133" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A133" s="53" t="s">
         <v>137</v>
       </c>
@@ -29981,7 +29961,7 @@
         <v>3874</v>
       </c>
     </row>
-    <row r="134" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="134" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A134" s="53" t="s">
         <v>46</v>
       </c>
@@ -30040,7 +30020,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="135" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="135" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A135" s="53" t="s">
         <v>110</v>
       </c>
@@ -30099,7 +30079,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="136" spans="1:19" s="70" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="136" s="70" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A136" s="63" t="s">
         <v>146</v>
       </c>
@@ -30158,7 +30138,7 @@
         <v>5043</v>
       </c>
     </row>
-    <row r="137" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="137" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A137" s="65"/>
       <c r="B137" s="15"/>
       <c r="C137" s="15"/>
@@ -30179,7 +30159,7 @@
       <c r="R137" s="15"/>
       <c r="S137" s="15"/>
     </row>
-    <row r="138" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="138" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A138" s="61" t="s">
         <v>158</v>
       </c>
@@ -30202,7 +30182,7 @@
       <c r="R138" s="15"/>
       <c r="S138" s="15"/>
     </row>
-    <row r="139" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="139" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A139" s="53" t="s">
         <v>136</v>
       </c>
@@ -30261,7 +30241,7 @@
         <v>3598</v>
       </c>
     </row>
-    <row r="140" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="140" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A140" s="53" t="s">
         <v>137</v>
       </c>
@@ -30320,7 +30300,7 @@
         <v>16023</v>
       </c>
     </row>
-    <row r="141" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="141" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A141" s="53" t="s">
         <v>46</v>
       </c>
@@ -30379,7 +30359,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="142" spans="1:19" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="142" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A142" s="53" t="s">
         <v>110</v>
       </c>
@@ -30438,7 +30418,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="143" spans="1:19" s="70" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="143" s="70" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A143" s="63" t="s">
         <v>146</v>
       </c>
@@ -30497,47 +30477,41 @@
         <v>19775</v>
       </c>
     </row>
-    <row r="144" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="145" spans="1:1" s="112" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" ht="15" customHeight="1" ns3:dyDescent="0.25"/>
+    <row r="145" s="112" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A145" s="112" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="146" spans="1:1" s="99" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" s="99" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A146" s="99" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="147" spans="1:1" s="119" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" s="119" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A147" s="119" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="148" spans="1:1" s="99" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" s="99" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A148" s="99" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="149" spans="1:1" s="99" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" s="99" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A149" s="99" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="150" spans="1:1" s="107" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" s="107" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A150" s="107" t="s">
         <v>9</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1"/>
-  <mergeCells count="16">
-    <mergeCell ref="A148:XFD148"/>
-    <mergeCell ref="A149:XFD149"/>
-    <mergeCell ref="A150:XFD150"/>
+  <mergeCells count="10">
     <mergeCell ref="A2:S2"/>
-    <mergeCell ref="A145:XFD145"/>
-    <mergeCell ref="A146:XFD146"/>
-    <mergeCell ref="A147:XFD147"/>
     <mergeCell ref="A1:S1"/>
     <mergeCell ref="B123:S123"/>
     <mergeCell ref="B45:S45"/>
@@ -30549,7 +30523,7 @@
     <mergeCell ref="A4:A5"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A150" r:id="rId1" location="copyright-and-creative-commons" xr:uid="{94ED34CA-95A0-4239-A31D-5897E7E1E931}"/>
+    <hyperlink ref="A150" r:id="rId1" location="copyright-and-creative-commons" ns2:uid="{94ED34CA-95A0-4239-A31D-5897E7E1E931}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
@@ -30558,12 +30532,12 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11D45E64-B625-45DD-BB47-04AAB4EF7566}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{11D45E64-B625-45DD-BB47-04AAB4EF7566}">
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
   <dimension ref="A1:S122"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" customHeight="1" zeroHeight="1" ns3:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="56.81640625" customWidth="1"/>
     <col min="2" max="3" width="16.453125" customWidth="1"/>
@@ -30582,7 +30556,7 @@
     <col min="18" max="19" width="11.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="73" customFormat="1" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" s="73" customFormat="1" ht="5.0999999999999996" customHeight="1" ns3:dyDescent="0.25">
       <c r="A1" s="105" t="s">
         <v>234</v>
       </c>
@@ -30605,7 +30579,7 @@
       <c r="R1" s="105"/>
       <c r="S1" s="105"/>
     </row>
-    <row r="2" spans="1:19" s="86" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" s="86" customFormat="1" ht="60" customHeight="1" ns3:dyDescent="0.25">
       <c r="A2" s="96" t="s">
         <v>1</v>
       </c>
@@ -30628,7 +30602,7 @@
       <c r="R2" s="96"/>
       <c r="S2" s="96"/>
     </row>
-    <row r="3" spans="1:19" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="3" ht="36" customHeight="1" thickBot="1" ns3:dyDescent="0.45">
       <c r="A3" s="113" t="s">
         <v>171</v>
       </c>
@@ -30651,7 +30625,7 @@
       <c r="R3" s="113"/>
       <c r="S3" s="113"/>
     </row>
-    <row r="4" spans="1:19" s="1" customFormat="1" ht="66.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="4" s="1" customFormat="1" ht="66.75" customHeight="1" thickTop="1" ns3:dyDescent="0.3">
       <c r="A4" s="118" t="s">
         <v>133</v>
       </c>
@@ -30710,7 +30684,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="5" spans="1:19" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" s="1" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A5" s="118"/>
       <c r="B5" s="120" t="s">
         <v>37</v>
@@ -30735,7 +30709,7 @@
       <c r="R5" s="120"/>
       <c r="S5" s="120"/>
     </row>
-    <row r="6" spans="1:19" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" s="1" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A6" s="60"/>
       <c r="B6" s="121" t="s">
         <v>63</v>
@@ -30758,7 +30732,7 @@
       <c r="R6" s="121"/>
       <c r="S6" s="121"/>
     </row>
-    <row r="7" spans="1:19" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" s="1" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A7" s="52" t="s">
         <v>39</v>
       </c>
@@ -30817,7 +30791,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="8" spans="1:19" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" s="1" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A8" s="52" t="s">
         <v>40</v>
       </c>
@@ -30876,7 +30850,7 @@
         <v>59908</v>
       </c>
     </row>
-    <row r="9" spans="1:19" s="81" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" s="81" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A9" s="65" t="s">
         <v>20</v>
       </c>
@@ -30935,7 +30909,7 @@
         <v>52226</v>
       </c>
     </row>
-    <row r="10" spans="1:19" s="81" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" s="81" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A10" s="65" t="s">
         <v>21</v>
       </c>
@@ -30994,7 +30968,7 @@
         <v>7684</v>
       </c>
     </row>
-    <row r="11" spans="1:19" s="81" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" s="81" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A11" s="82" t="s">
         <v>147</v>
       </c>
@@ -31053,7 +31027,7 @@
         <v>7561</v>
       </c>
     </row>
-    <row r="12" spans="1:19" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" s="1" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A12" s="52" t="s">
         <v>41</v>
       </c>
@@ -31112,7 +31086,7 @@
         <v>4614</v>
       </c>
     </row>
-    <row r="13" spans="1:19" s="81" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" s="81" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A13" s="83" t="s">
         <v>22</v>
       </c>
@@ -31171,7 +31145,7 @@
         <v>2872</v>
       </c>
     </row>
-    <row r="14" spans="1:19" s="81" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" s="81" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A14" s="82" t="s">
         <v>71</v>
       </c>
@@ -31230,7 +31204,7 @@
         <v>1947</v>
       </c>
     </row>
-    <row r="15" spans="1:19" s="81" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" s="81" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A15" s="82" t="s">
         <v>72</v>
       </c>
@@ -31289,7 +31263,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="16" spans="1:19" s="81" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" s="81" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A16" s="65" t="s">
         <v>134</v>
       </c>
@@ -31348,7 +31322,7 @@
         <v>1736</v>
       </c>
     </row>
-    <row r="17" spans="1:19" s="81" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" s="81" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A17" s="82" t="s">
         <v>74</v>
       </c>
@@ -31407,7 +31381,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="18" spans="1:19" s="81" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" s="81" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A18" s="82" t="s">
         <v>75</v>
       </c>
@@ -31466,7 +31440,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="19" spans="1:19" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" s="1" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A19" s="67" t="s">
         <v>76</v>
       </c>
@@ -31525,7 +31499,7 @@
         <v>20722</v>
       </c>
     </row>
-    <row r="20" spans="1:19" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" s="1" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A20" s="67" t="s">
         <v>148</v>
       </c>
@@ -31584,7 +31558,7 @@
         <v>4639</v>
       </c>
     </row>
-    <row r="21" spans="1:19" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" s="1" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A21" s="67" t="s">
         <v>23</v>
       </c>
@@ -31643,7 +31617,7 @@
         <v>2848</v>
       </c>
     </row>
-    <row r="22" spans="1:19" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" s="1" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A22" s="67" t="s">
         <v>24</v>
       </c>
@@ -31702,7 +31676,7 @@
         <v>10712</v>
       </c>
     </row>
-    <row r="23" spans="1:19" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" s="1" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A23" s="67" t="s">
         <v>78</v>
       </c>
@@ -31761,7 +31735,7 @@
         <v>37897</v>
       </c>
     </row>
-    <row r="24" spans="1:19" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" s="1" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A24" s="67" t="s">
         <v>42</v>
       </c>
@@ -31820,7 +31794,7 @@
         <v>8189</v>
       </c>
     </row>
-    <row r="25" spans="1:19" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" s="1" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A25" s="52" t="s">
         <v>43</v>
       </c>
@@ -31879,7 +31853,7 @@
         <v>35048</v>
       </c>
     </row>
-    <row r="26" spans="1:19" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" s="1" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A26" s="67" t="s">
         <v>30</v>
       </c>
@@ -31938,7 +31912,7 @@
         <v>12653</v>
       </c>
     </row>
-    <row r="27" spans="1:19" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" s="1" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A27" s="52" t="s">
         <v>31</v>
       </c>
@@ -31997,7 +31971,7 @@
         <v>14107</v>
       </c>
     </row>
-    <row r="28" spans="1:19" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" s="1" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A28" s="52" t="s">
         <v>44</v>
       </c>
@@ -32056,7 +32030,7 @@
         <v>16778</v>
       </c>
     </row>
-    <row r="29" spans="1:19" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" s="1" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A29" s="52" t="s">
         <v>135</v>
       </c>
@@ -32115,7 +32089,7 @@
         <v>165524</v>
       </c>
     </row>
-    <row r="30" spans="1:19" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" s="1" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A30" s="68" t="s">
         <v>203</v>
       </c>
@@ -32174,7 +32148,7 @@
         <v>44752</v>
       </c>
     </row>
-    <row r="31" spans="1:19" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" s="1" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A31" s="52" t="s">
         <v>35</v>
       </c>
@@ -32233,7 +32207,7 @@
         <v>8352</v>
       </c>
     </row>
-    <row r="32" spans="1:19" s="1" customFormat="1" ht="25.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" s="1" customFormat="1" ht="25.65" customHeight="1" ns3:dyDescent="0.3">
       <c r="A32" s="69" t="s">
         <v>150</v>
       </c>
@@ -32292,7 +32266,7 @@
         <v>447122</v>
       </c>
     </row>
-    <row r="33" spans="1:19" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" s="1" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A33" s="60"/>
       <c r="B33" s="116" t="s">
         <v>97</v>
@@ -32315,7 +32289,7 @@
       <c r="R33" s="116"/>
       <c r="S33" s="116"/>
     </row>
-    <row r="34" spans="1:19" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" s="1" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A34" s="52" t="s">
         <v>39</v>
       </c>
@@ -32374,7 +32348,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="35" spans="1:19" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" s="1" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A35" s="52" t="s">
         <v>40</v>
       </c>
@@ -32433,7 +32407,7 @@
         <v>2536</v>
       </c>
     </row>
-    <row r="36" spans="1:19" s="81" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" s="81" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A36" s="65" t="s">
         <v>20</v>
       </c>
@@ -32492,7 +32466,7 @@
         <v>2363</v>
       </c>
     </row>
-    <row r="37" spans="1:19" s="81" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" s="81" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A37" s="65" t="s">
         <v>21</v>
       </c>
@@ -32551,7 +32525,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="38" spans="1:19" s="81" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" s="81" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A38" s="82" t="s">
         <v>147</v>
       </c>
@@ -32610,7 +32584,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="39" spans="1:19" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" s="1" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A39" s="52" t="s">
         <v>41</v>
       </c>
@@ -32669,7 +32643,7 @@
         <v>2495</v>
       </c>
     </row>
-    <row r="40" spans="1:19" s="81" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" s="81" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A40" s="83" t="s">
         <v>22</v>
       </c>
@@ -32728,7 +32702,7 @@
         <v>1710</v>
       </c>
     </row>
-    <row r="41" spans="1:19" s="81" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" s="81" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A41" s="82" t="s">
         <v>71</v>
       </c>
@@ -32787,7 +32761,7 @@
         <v>1553</v>
       </c>
     </row>
-    <row r="42" spans="1:19" s="81" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" s="81" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A42" s="82" t="s">
         <v>72</v>
       </c>
@@ -32846,7 +32820,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="43" spans="1:19" s="81" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" s="81" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A43" s="65" t="s">
         <v>134</v>
       </c>
@@ -32905,7 +32879,7 @@
         <v>784</v>
       </c>
     </row>
-    <row r="44" spans="1:19" s="81" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" s="81" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A44" s="82" t="s">
         <v>74</v>
       </c>
@@ -32964,7 +32938,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="45" spans="1:19" s="81" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" s="81" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A45" s="82" t="s">
         <v>75</v>
       </c>
@@ -33023,7 +32997,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="46" spans="1:19" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" s="1" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A46" s="67" t="s">
         <v>76</v>
       </c>
@@ -33082,7 +33056,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="47" spans="1:19" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" s="1" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A47" s="67" t="s">
         <v>148</v>
       </c>
@@ -33141,7 +33115,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="48" spans="1:19" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" s="1" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A48" s="67" t="s">
         <v>23</v>
       </c>
@@ -33200,7 +33174,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="49" spans="1:19" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" s="1" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A49" s="67" t="s">
         <v>24</v>
       </c>
@@ -33259,7 +33233,7 @@
         <v>1071</v>
       </c>
     </row>
-    <row r="50" spans="1:19" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" s="1" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A50" s="67" t="s">
         <v>78</v>
       </c>
@@ -33318,7 +33292,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="51" spans="1:19" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" s="1" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A51" s="67" t="s">
         <v>42</v>
       </c>
@@ -33377,7 +33351,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="52" spans="1:19" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" s="1" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A52" s="52" t="s">
         <v>43</v>
       </c>
@@ -33436,7 +33410,7 @@
         <v>2760</v>
       </c>
     </row>
-    <row r="53" spans="1:19" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" s="1" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A53" s="67" t="s">
         <v>30</v>
       </c>
@@ -33495,7 +33469,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="54" spans="1:19" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" s="1" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A54" s="52" t="s">
         <v>31</v>
       </c>
@@ -33554,7 +33528,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="55" spans="1:19" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" s="1" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A55" s="52" t="s">
         <v>44</v>
       </c>
@@ -33613,7 +33587,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="56" spans="1:19" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" s="1" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A56" s="52" t="s">
         <v>135</v>
       </c>
@@ -33672,7 +33646,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="57" spans="1:19" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" s="1" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A57" s="68" t="s">
         <v>203</v>
       </c>
@@ -33731,7 +33705,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="58" spans="1:19" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" s="1" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A58" s="52" t="s">
         <v>35</v>
       </c>
@@ -33790,7 +33764,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="59" spans="1:19" s="1" customFormat="1" ht="25.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" s="1" customFormat="1" ht="25.65" customHeight="1" ns3:dyDescent="0.3">
       <c r="A59" s="69" t="s">
         <v>150</v>
       </c>
@@ -33849,7 +33823,7 @@
         <v>12763</v>
       </c>
     </row>
-    <row r="60" spans="1:19" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" s="1" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A60" s="60"/>
       <c r="B60" s="116" t="s">
         <v>98</v>
@@ -33872,7 +33846,7 @@
       <c r="R60" s="116"/>
       <c r="S60" s="116"/>
     </row>
-    <row r="61" spans="1:19" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" s="1" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A61" s="52" t="s">
         <v>39</v>
       </c>
@@ -33931,7 +33905,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="62" spans="1:19" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" s="1" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A62" s="52" t="s">
         <v>40</v>
       </c>
@@ -33990,7 +33964,7 @@
         <v>52637</v>
       </c>
     </row>
-    <row r="63" spans="1:19" s="81" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" s="81" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A63" s="65" t="s">
         <v>20</v>
       </c>
@@ -34049,7 +34023,7 @@
         <v>45550</v>
       </c>
     </row>
-    <row r="64" spans="1:19" s="81" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" s="81" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A64" s="65" t="s">
         <v>21</v>
       </c>
@@ -34108,7 +34082,7 @@
         <v>7084</v>
       </c>
     </row>
-    <row r="65" spans="1:19" s="81" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" s="81" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A65" s="82" t="s">
         <v>147</v>
       </c>
@@ -34167,7 +34141,7 @@
         <v>6992</v>
       </c>
     </row>
-    <row r="66" spans="1:19" s="81" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" s="81" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A66" s="84" t="s">
         <v>41</v>
       </c>
@@ -34226,7 +34200,7 @@
         <v>1888</v>
       </c>
     </row>
-    <row r="67" spans="1:19" s="81" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" s="81" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A67" s="83" t="s">
         <v>22</v>
       </c>
@@ -34285,7 +34259,7 @@
         <v>985</v>
       </c>
     </row>
-    <row r="68" spans="1:19" s="81" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" s="81" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A68" s="82" t="s">
         <v>71</v>
       </c>
@@ -34344,7 +34318,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="69" spans="1:19" s="81" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" s="81" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A69" s="82" t="s">
         <v>72</v>
       </c>
@@ -34403,7 +34377,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="70" spans="1:19" s="81" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" s="81" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A70" s="65" t="s">
         <v>134</v>
       </c>
@@ -34462,7 +34436,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="71" spans="1:19" s="81" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" s="81" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A71" s="82" t="s">
         <v>74</v>
       </c>
@@ -34521,7 +34495,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="72" spans="1:19" s="81" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" s="81" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A72" s="82" t="s">
         <v>75</v>
       </c>
@@ -34580,7 +34554,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="73" spans="1:19" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" s="1" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A73" s="67" t="s">
         <v>76</v>
       </c>
@@ -34639,7 +34613,7 @@
         <v>19412</v>
       </c>
     </row>
-    <row r="74" spans="1:19" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" s="1" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A74" s="67" t="s">
         <v>148</v>
       </c>
@@ -34698,7 +34672,7 @@
         <v>4190</v>
       </c>
     </row>
-    <row r="75" spans="1:19" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" s="1" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A75" s="67" t="s">
         <v>23</v>
       </c>
@@ -34757,7 +34731,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="76" spans="1:19" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" s="1" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A76" s="67" t="s">
         <v>24</v>
       </c>
@@ -34816,7 +34790,7 @@
         <v>6703</v>
       </c>
     </row>
-    <row r="77" spans="1:19" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" s="1" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A77" s="67" t="s">
         <v>78</v>
       </c>
@@ -34875,7 +34849,7 @@
         <v>33465</v>
       </c>
     </row>
-    <row r="78" spans="1:19" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" s="1" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A78" s="67" t="s">
         <v>42</v>
       </c>
@@ -34934,7 +34908,7 @@
         <v>7638</v>
       </c>
     </row>
-    <row r="79" spans="1:19" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" s="1" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A79" s="52" t="s">
         <v>43</v>
       </c>
@@ -34993,7 +34967,7 @@
         <v>31693</v>
       </c>
     </row>
-    <row r="80" spans="1:19" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" s="1" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A80" s="67" t="s">
         <v>30</v>
       </c>
@@ -35052,7 +35026,7 @@
         <v>11709</v>
       </c>
     </row>
-    <row r="81" spans="1:19" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" s="1" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A81" s="52" t="s">
         <v>31</v>
       </c>
@@ -35111,7 +35085,7 @@
         <v>12692</v>
       </c>
     </row>
-    <row r="82" spans="1:19" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" s="1" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A82" s="52" t="s">
         <v>44</v>
       </c>
@@ -35170,7 +35144,7 @@
         <v>15904</v>
       </c>
     </row>
-    <row r="83" spans="1:19" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" s="1" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A83" s="52" t="s">
         <v>135</v>
       </c>
@@ -35229,7 +35203,7 @@
         <v>164242</v>
       </c>
     </row>
-    <row r="84" spans="1:19" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" s="1" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A84" s="68" t="s">
         <v>203</v>
       </c>
@@ -35288,7 +35262,7 @@
         <v>43889</v>
       </c>
     </row>
-    <row r="85" spans="1:19" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" s="1" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A85" s="52" t="s">
         <v>35</v>
       </c>
@@ -35347,7 +35321,7 @@
         <v>8199</v>
       </c>
     </row>
-    <row r="86" spans="1:19" s="1" customFormat="1" ht="25.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" s="1" customFormat="1" ht="25.65" customHeight="1" ns3:dyDescent="0.3">
       <c r="A86" s="69" t="s">
         <v>150</v>
       </c>
@@ -35406,7 +35380,7 @@
         <v>414586</v>
       </c>
     </row>
-    <row r="87" spans="1:19" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" s="1" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A87" s="60"/>
       <c r="B87" s="116" t="s">
         <v>99</v>
@@ -35429,7 +35403,7 @@
       <c r="R87" s="116"/>
       <c r="S87" s="116"/>
     </row>
-    <row r="88" spans="1:19" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" s="1" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A88" s="52" t="s">
         <v>39</v>
       </c>
@@ -35488,7 +35462,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="89" spans="1:19" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" s="1" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A89" s="52" t="s">
         <v>40</v>
       </c>
@@ -35547,7 +35521,7 @@
         <v>4739</v>
       </c>
     </row>
-    <row r="90" spans="1:19" s="81" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" s="81" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A90" s="65" t="s">
         <v>20</v>
       </c>
@@ -35606,7 +35580,7 @@
         <v>4314</v>
       </c>
     </row>
-    <row r="91" spans="1:19" s="81" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" s="81" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A91" s="65" t="s">
         <v>21</v>
       </c>
@@ -35665,7 +35639,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="92" spans="1:19" s="81" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" s="81" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A92" s="82" t="s">
         <v>147</v>
       </c>
@@ -35724,7 +35698,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="93" spans="1:19" s="81" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" s="81" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A93" s="84" t="s">
         <v>41</v>
       </c>
@@ -35783,7 +35757,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="94" spans="1:19" s="81" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" s="81" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A94" s="83" t="s">
         <v>22</v>
       </c>
@@ -35842,7 +35816,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="95" spans="1:19" s="81" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" s="81" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A95" s="82" t="s">
         <v>71</v>
       </c>
@@ -35901,7 +35875,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="96" spans="1:19" s="81" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" s="81" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A96" s="82" t="s">
         <v>72</v>
       </c>
@@ -35960,7 +35934,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="97" spans="1:19" s="81" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" s="81" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A97" s="65" t="s">
         <v>134</v>
       </c>
@@ -36019,7 +35993,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="98" spans="1:19" s="81" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" s="81" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A98" s="82" t="s">
         <v>74</v>
       </c>
@@ -36078,7 +36052,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="99" spans="1:19" s="81" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" s="81" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A99" s="82" t="s">
         <v>75</v>
       </c>
@@ -36137,7 +36111,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="100" spans="1:19" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" s="1" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A100" s="67" t="s">
         <v>76</v>
       </c>
@@ -36196,7 +36170,7 @@
         <v>985</v>
       </c>
     </row>
-    <row r="101" spans="1:19" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" s="1" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A101" s="67" t="s">
         <v>148</v>
       </c>
@@ -36255,7 +36229,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="102" spans="1:19" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" s="1" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A102" s="67" t="s">
         <v>23</v>
       </c>
@@ -36314,7 +36288,7 @@
         <v>1331</v>
       </c>
     </row>
-    <row r="103" spans="1:19" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" s="1" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A103" s="67" t="s">
         <v>24</v>
       </c>
@@ -36373,7 +36347,7 @@
         <v>2940</v>
       </c>
     </row>
-    <row r="104" spans="1:19" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" s="1" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A104" s="67" t="s">
         <v>78</v>
       </c>
@@ -36432,7 +36406,7 @@
         <v>4069</v>
       </c>
     </row>
-    <row r="105" spans="1:19" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" s="1" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A105" s="67" t="s">
         <v>42</v>
       </c>
@@ -36491,7 +36465,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="106" spans="1:19" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" s="1" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A106" s="52" t="s">
         <v>43</v>
       </c>
@@ -36550,7 +36524,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="107" spans="1:19" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" s="1" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A107" s="67" t="s">
         <v>30</v>
       </c>
@@ -36609,7 +36583,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="108" spans="1:19" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" s="1" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A108" s="52" t="s">
         <v>31</v>
       </c>
@@ -36668,7 +36642,7 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="109" spans="1:19" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" s="1" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A109" s="52" t="s">
         <v>44</v>
       </c>
@@ -36727,7 +36701,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="110" spans="1:19" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" s="1" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A110" s="52" t="s">
         <v>135</v>
       </c>
@@ -36786,7 +36760,7 @@
         <v>1233</v>
       </c>
     </row>
-    <row r="111" spans="1:19" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" s="1" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A111" s="68" t="s">
         <v>203</v>
       </c>
@@ -36845,7 +36819,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="112" spans="1:19" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" s="1" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A112" s="52" t="s">
         <v>35</v>
       </c>
@@ -36904,7 +36878,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="113" spans="1:19" s="1" customFormat="1" ht="25.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" s="1" customFormat="1" ht="25.65" customHeight="1" ns3:dyDescent="0.3">
       <c r="A113" s="69" t="s">
         <v>150</v>
       </c>
@@ -36963,53 +36937,50 @@
         <v>19775</v>
       </c>
     </row>
-    <row r="114" spans="1:19" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="115" spans="1:19" s="112" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" s="1" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.25"/>
+    <row r="115" s="112" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A115" s="112" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="116" spans="1:19" s="119" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" s="119" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A116" s="119" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="117" spans="1:19" s="119" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" s="119" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A117" s="119" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="118" spans="1:19" s="114" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" s="114" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A118" s="114" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="119" spans="1:19" s="114" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" s="114" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A119" s="114" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="120" spans="1:19" s="119" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" s="119" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A120" s="119" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="121" spans="1:19" s="99" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" s="99" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A121" s="99" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="122" spans="1:19" s="107" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" s="107" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A122" s="107" t="s">
         <v>9</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1"/>
-  <mergeCells count="18">
-    <mergeCell ref="A115:XFD115"/>
-    <mergeCell ref="A116:XFD116"/>
-    <mergeCell ref="A117:XFD117"/>
+  <mergeCells count="10">
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="A1:S1"/>
     <mergeCell ref="B33:S33"/>
@@ -37020,14 +36991,9 @@
     <mergeCell ref="B6:S6"/>
     <mergeCell ref="A3:S3"/>
     <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A118:XFD118"/>
-    <mergeCell ref="A119:XFD119"/>
-    <mergeCell ref="A120:XFD120"/>
-    <mergeCell ref="A121:XFD121"/>
-    <mergeCell ref="A122:XFD122"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A122" r:id="rId1" location="copyright-and-creative-commons" xr:uid="{71D886B3-7673-420A-B5C5-60032D4A6EE4}"/>
+    <hyperlink ref="A122" r:id="rId1" location="copyright-and-creative-commons" ns2:uid="{71D886B3-7673-420A-B5C5-60032D4A6EE4}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
@@ -37036,12 +37002,12 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F06339AE-1AA7-4425-9B9D-F2C353973BF9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{F06339AE-1AA7-4425-9B9D-F2C353973BF9}">
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
   <dimension ref="A1:Q84"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" customHeight="1" zeroHeight="1" ns3:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="51.1796875" customWidth="1"/>
     <col min="2" max="2" width="11.453125" customWidth="1"/>
@@ -37051,7 +37017,7 @@
     <col min="14" max="17" width="11.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="73" customFormat="1" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" s="73" customFormat="1" ht="5.0999999999999996" customHeight="1" ns3:dyDescent="0.25">
       <c r="A1" s="105" t="s">
         <v>213</v>
       </c>
@@ -37072,7 +37038,7 @@
       <c r="P1" s="105"/>
       <c r="Q1" s="105"/>
     </row>
-    <row r="2" spans="1:17" s="86" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" s="86" customFormat="1" ht="60" customHeight="1" ns3:dyDescent="0.25">
       <c r="A2" s="96" t="s">
         <v>1</v>
       </c>
@@ -37093,7 +37059,7 @@
       <c r="P2" s="96"/>
       <c r="Q2" s="96"/>
     </row>
-    <row r="3" spans="1:17" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="3" ht="36" customHeight="1" thickBot="1" ns3:dyDescent="0.45">
       <c r="A3" s="113" t="s">
         <v>126</v>
       </c>
@@ -37114,7 +37080,7 @@
       <c r="P3" s="113"/>
       <c r="Q3" s="113"/>
     </row>
-    <row r="4" spans="1:17" s="12" customFormat="1" ht="44.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="4" s="12" customFormat="1" ht="44.25" customHeight="1" thickTop="1" ns3:dyDescent="0.3">
       <c r="A4" s="118" t="s">
         <v>133</v>
       </c>
@@ -37167,7 +37133,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="5" spans="1:17" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A5" s="118"/>
       <c r="B5" s="122" t="s">
         <v>37</v>
@@ -37190,7 +37156,7 @@
       <c r="P5" s="122"/>
       <c r="Q5" s="122"/>
     </row>
-    <row r="6" spans="1:17" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A6" s="60"/>
       <c r="B6" s="123" t="s">
         <v>63</v>
@@ -37211,7 +37177,7 @@
       <c r="P6" s="123"/>
       <c r="Q6" s="123"/>
     </row>
-    <row r="7" spans="1:17" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A7" s="52" t="s">
         <v>39</v>
       </c>
@@ -37264,7 +37230,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="8" spans="1:17" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A8" s="52" t="s">
         <v>151</v>
       </c>
@@ -37317,7 +37283,7 @@
         <v>16.3</v>
       </c>
     </row>
-    <row r="9" spans="1:17" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A9" s="52" t="s">
         <v>41</v>
       </c>
@@ -37370,7 +37336,7 @@
         <v>40.1</v>
       </c>
     </row>
-    <row r="10" spans="1:17" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A10" s="67" t="s">
         <v>76</v>
       </c>
@@ -37423,7 +37389,7 @@
         <v>9.1</v>
       </c>
     </row>
-    <row r="11" spans="1:17" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A11" s="67" t="s">
         <v>152</v>
       </c>
@@ -37476,7 +37442,7 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="12" spans="1:17" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A12" s="67" t="s">
         <v>23</v>
       </c>
@@ -37529,7 +37495,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:17" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A13" s="67" t="s">
         <v>24</v>
       </c>
@@ -37582,7 +37548,7 @@
         <v>18.399999999999999</v>
       </c>
     </row>
-    <row r="14" spans="1:17" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A14" s="67" t="s">
         <v>78</v>
       </c>
@@ -37635,7 +37601,7 @@
         <v>5.7</v>
       </c>
     </row>
-    <row r="15" spans="1:17" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A15" s="67" t="s">
         <v>42</v>
       </c>
@@ -37688,7 +37654,7 @@
         <v>13.1</v>
       </c>
     </row>
-    <row r="16" spans="1:17" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A16" s="52" t="s">
         <v>43</v>
       </c>
@@ -37741,7 +37707,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="17" spans="1:17" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A17" s="67" t="s">
         <v>30</v>
       </c>
@@ -37794,7 +37760,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:17" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A18" s="52" t="s">
         <v>31</v>
       </c>
@@ -37847,7 +37813,7 @@
         <v>7.1</v>
       </c>
     </row>
-    <row r="19" spans="1:17" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A19" s="52" t="s">
         <v>44</v>
       </c>
@@ -37900,7 +37866,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:17" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A20" s="52" t="s">
         <v>135</v>
       </c>
@@ -37953,7 +37919,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="21" spans="1:17" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A21" s="68" t="s">
         <v>153</v>
       </c>
@@ -38006,7 +37972,7 @@
         <v>4.7</v>
       </c>
     </row>
-    <row r="22" spans="1:17" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A22" s="52" t="s">
         <v>35</v>
       </c>
@@ -38059,7 +38025,7 @@
         <v>6.9</v>
       </c>
     </row>
-    <row r="23" spans="1:17" s="12" customFormat="1" ht="25.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" s="12" customFormat="1" ht="25.65" customHeight="1" ns3:dyDescent="0.3">
       <c r="A23" s="69" t="s">
         <v>154</v>
       </c>
@@ -38112,7 +38078,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="24" spans="1:17" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A24" s="60"/>
       <c r="B24" s="116" t="s">
         <v>97</v>
@@ -38133,7 +38099,7 @@
       <c r="P24" s="116"/>
       <c r="Q24" s="116"/>
     </row>
-    <row r="25" spans="1:17" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A25" s="52" t="s">
         <v>39</v>
       </c>
@@ -38186,7 +38152,7 @@
         <v>63.9</v>
       </c>
     </row>
-    <row r="26" spans="1:17" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A26" s="52" t="s">
         <v>151</v>
       </c>
@@ -38239,7 +38205,7 @@
         <v>37.1</v>
       </c>
     </row>
-    <row r="27" spans="1:17" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A27" s="52" t="s">
         <v>41</v>
       </c>
@@ -38292,7 +38258,7 @@
         <v>48.1</v>
       </c>
     </row>
-    <row r="28" spans="1:17" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A28" s="67" t="s">
         <v>76</v>
       </c>
@@ -38345,7 +38311,7 @@
         <v>35.9</v>
       </c>
     </row>
-    <row r="29" spans="1:17" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A29" s="67" t="s">
         <v>152</v>
       </c>
@@ -38398,7 +38364,7 @@
         <v>41.9</v>
       </c>
     </row>
-    <row r="30" spans="1:17" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A30" s="67" t="s">
         <v>23</v>
       </c>
@@ -38451,7 +38417,7 @@
         <v>29.1</v>
       </c>
     </row>
-    <row r="31" spans="1:17" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A31" s="67" t="s">
         <v>24</v>
       </c>
@@ -38504,7 +38470,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="32" spans="1:17" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A32" s="67" t="s">
         <v>78</v>
       </c>
@@ -38557,7 +38523,7 @@
         <v>39.4</v>
       </c>
     </row>
-    <row r="33" spans="1:17" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A33" s="67" t="s">
         <v>42</v>
       </c>
@@ -38610,7 +38576,7 @@
         <v>57.7</v>
       </c>
     </row>
-    <row r="34" spans="1:17" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A34" s="52" t="s">
         <v>43</v>
       </c>
@@ -38663,7 +38629,7 @@
         <v>36.4</v>
       </c>
     </row>
-    <row r="35" spans="1:17" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A35" s="67" t="s">
         <v>30</v>
       </c>
@@ -38716,7 +38682,7 @@
         <v>29.3</v>
       </c>
     </row>
-    <row r="36" spans="1:17" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A36" s="52" t="s">
         <v>31</v>
       </c>
@@ -38769,7 +38735,7 @@
         <v>32.299999999999997</v>
       </c>
     </row>
-    <row r="37" spans="1:17" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A37" s="52" t="s">
         <v>44</v>
       </c>
@@ -38822,7 +38788,7 @@
         <v>33.200000000000003</v>
       </c>
     </row>
-    <row r="38" spans="1:17" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A38" s="52" t="s">
         <v>135</v>
       </c>
@@ -38875,7 +38841,7 @@
         <v>34.6</v>
       </c>
     </row>
-    <row r="39" spans="1:17" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A39" s="68" t="s">
         <v>153</v>
       </c>
@@ -38928,7 +38894,7 @@
         <v>36.799999999999997</v>
       </c>
     </row>
-    <row r="40" spans="1:17" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A40" s="52" t="s">
         <v>35</v>
       </c>
@@ -38981,7 +38947,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="41" spans="1:17" s="12" customFormat="1" ht="25.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" s="12" customFormat="1" ht="25.65" customHeight="1" ns3:dyDescent="0.3">
       <c r="A41" s="69" t="s">
         <v>154</v>
       </c>
@@ -39034,7 +39000,7 @@
         <v>37.9</v>
       </c>
     </row>
-    <row r="42" spans="1:17" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A42" s="60"/>
       <c r="B42" s="116" t="s">
         <v>98</v>
@@ -39055,7 +39021,7 @@
       <c r="P42" s="116"/>
       <c r="Q42" s="116"/>
     </row>
-    <row r="43" spans="1:17" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A43" s="52" t="s">
         <v>39</v>
       </c>
@@ -39108,7 +39074,7 @@
         <v>28.9</v>
       </c>
     </row>
-    <row r="44" spans="1:17" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A44" s="52" t="s">
         <v>151</v>
       </c>
@@ -39161,7 +39127,7 @@
         <v>15.4</v>
       </c>
     </row>
-    <row r="45" spans="1:17" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A45" s="52" t="s">
         <v>41</v>
       </c>
@@ -39214,7 +39180,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="46" spans="1:17" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A46" s="67" t="s">
         <v>76</v>
       </c>
@@ -39267,7 +39233,7 @@
         <v>8.9</v>
       </c>
     </row>
-    <row r="47" spans="1:17" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A47" s="67" t="s">
         <v>152</v>
       </c>
@@ -39320,7 +39286,7 @@
         <v>11.3</v>
       </c>
     </row>
-    <row r="48" spans="1:17" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A48" s="67" t="s">
         <v>23</v>
       </c>
@@ -39373,7 +39339,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="49" spans="1:17" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A49" s="67" t="s">
         <v>24</v>
       </c>
@@ -39426,7 +39392,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="50" spans="1:17" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A50" s="67" t="s">
         <v>78</v>
       </c>
@@ -39479,7 +39445,7 @@
         <v>5.7</v>
       </c>
     </row>
-    <row r="51" spans="1:17" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A51" s="67" t="s">
         <v>42</v>
       </c>
@@ -39532,7 +39498,7 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="52" spans="1:17" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A52" s="52" t="s">
         <v>43</v>
       </c>
@@ -39585,7 +39551,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="53" spans="1:17" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A53" s="67" t="s">
         <v>30</v>
       </c>
@@ -39638,7 +39604,7 @@
         <v>8.4</v>
       </c>
     </row>
-    <row r="54" spans="1:17" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A54" s="52" t="s">
         <v>31</v>
       </c>
@@ -39691,7 +39657,7 @@
         <v>6.9</v>
       </c>
     </row>
-    <row r="55" spans="1:17" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A55" s="52" t="s">
         <v>44</v>
       </c>
@@ -39744,7 +39710,7 @@
         <v>4.9000000000000004</v>
       </c>
     </row>
-    <row r="56" spans="1:17" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A56" s="52" t="s">
         <v>135</v>
       </c>
@@ -39797,7 +39763,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="57" spans="1:17" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A57" s="68" t="s">
         <v>153</v>
       </c>
@@ -39850,7 +39816,7 @@
         <v>4.5999999999999996</v>
       </c>
     </row>
-    <row r="58" spans="1:17" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A58" s="52" t="s">
         <v>35</v>
       </c>
@@ -39903,7 +39869,7 @@
         <v>6.6</v>
       </c>
     </row>
-    <row r="59" spans="1:17" s="12" customFormat="1" ht="25.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" s="12" customFormat="1" ht="25.65" customHeight="1" ns3:dyDescent="0.3">
       <c r="A59" s="69" t="s">
         <v>154</v>
       </c>
@@ -39956,7 +39922,7 @@
         <v>6.1</v>
       </c>
     </row>
-    <row r="60" spans="1:17" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A60" s="60"/>
       <c r="B60" s="116" t="s">
         <v>99</v>
@@ -39977,7 +39943,7 @@
       <c r="P60" s="116"/>
       <c r="Q60" s="116"/>
     </row>
-    <row r="61" spans="1:17" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A61" s="52" t="s">
         <v>39</v>
       </c>
@@ -40030,7 +39996,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="62" spans="1:17" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A62" s="52" t="s">
         <v>151</v>
       </c>
@@ -40083,7 +40049,7 @@
         <v>14.6</v>
       </c>
     </row>
-    <row r="63" spans="1:17" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A63" s="52" t="s">
         <v>41</v>
       </c>
@@ -40136,7 +40102,7 @@
         <v>38.1</v>
       </c>
     </row>
-    <row r="64" spans="1:17" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A64" s="67" t="s">
         <v>76</v>
       </c>
@@ -40189,7 +40155,7 @@
         <v>10.1</v>
       </c>
     </row>
-    <row r="65" spans="1:17" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A65" s="67" t="s">
         <v>152</v>
       </c>
@@ -40242,7 +40208,7 @@
         <v>11.1</v>
       </c>
     </row>
-    <row r="66" spans="1:17" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A66" s="67" t="s">
         <v>23</v>
       </c>
@@ -40295,7 +40261,7 @@
         <v>18.899999999999999</v>
       </c>
     </row>
-    <row r="67" spans="1:17" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A67" s="67" t="s">
         <v>24</v>
       </c>
@@ -40348,7 +40314,7 @@
         <v>9.1</v>
       </c>
     </row>
-    <row r="68" spans="1:17" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A68" s="67" t="s">
         <v>78</v>
       </c>
@@ -40401,7 +40367,7 @@
         <v>4.5999999999999996</v>
       </c>
     </row>
-    <row r="69" spans="1:17" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A69" s="67" t="s">
         <v>42</v>
       </c>
@@ -40454,7 +40420,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="70" spans="1:17" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A70" s="52" t="s">
         <v>43</v>
       </c>
@@ -40507,7 +40473,7 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="71" spans="1:17" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A71" s="67" t="s">
         <v>30</v>
       </c>
@@ -40560,7 +40526,7 @@
         <v>10.3</v>
       </c>
     </row>
-    <row r="72" spans="1:17" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A72" s="52" t="s">
         <v>31</v>
       </c>
@@ -40613,7 +40579,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="73" spans="1:17" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A73" s="52" t="s">
         <v>44</v>
       </c>
@@ -40666,7 +40632,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="74" spans="1:17" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A74" s="52" t="s">
         <v>135</v>
       </c>
@@ -40719,7 +40685,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="75" spans="1:17" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A75" s="68" t="s">
         <v>153</v>
       </c>
@@ -40772,7 +40738,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="76" spans="1:17" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" s="12" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.3">
       <c r="A76" s="52" t="s">
         <v>35</v>
       </c>
@@ -40825,7 +40791,7 @@
         <v>8.4</v>
       </c>
     </row>
-    <row r="77" spans="1:17" s="12" customFormat="1" ht="25.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" s="12" customFormat="1" ht="25.65" customHeight="1" ns3:dyDescent="0.3">
       <c r="A77" s="69" t="s">
         <v>154</v>
       </c>
@@ -40878,43 +40844,41 @@
         <v>9.3000000000000007</v>
       </c>
     </row>
-    <row r="78" spans="1:17" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="79" spans="1:17" s="112" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" s="1" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.25"/>
+    <row r="79" s="112" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A79" s="112" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="80" spans="1:17" s="114" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" s="114" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A80" s="114" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="81" spans="1:1" s="114" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" s="114" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A81" s="114" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="82" spans="1:1" s="111" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" s="111" customFormat="1" ht="30" customHeight="1" ns3:dyDescent="0.25">
       <c r="A82" s="111" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="83" spans="1:1" s="99" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" s="99" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A83" s="99" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="84" spans="1:1" s="107" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" s="107" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A84" s="107" t="s">
         <v>9</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1"/>
-  <mergeCells count="16">
+  <mergeCells count="10">
     <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A83:XFD83"/>
-    <mergeCell ref="A84:XFD84"/>
     <mergeCell ref="A2:Q2"/>
     <mergeCell ref="A1:Q1"/>
     <mergeCell ref="B24:Q24"/>
@@ -40924,13 +40888,9 @@
     <mergeCell ref="J5:Q5"/>
     <mergeCell ref="B6:Q6"/>
     <mergeCell ref="A3:Q3"/>
-    <mergeCell ref="A79:XFD79"/>
-    <mergeCell ref="A80:XFD80"/>
-    <mergeCell ref="A81:XFD81"/>
-    <mergeCell ref="A82:XFD82"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A84" r:id="rId1" location="copyright-and-creative-commons" xr:uid="{C4DD00FB-4E4E-4EB6-8BB2-F344FFBC7CED}"/>
+    <hyperlink ref="A84" r:id="rId1" location="copyright-and-creative-commons" ns2:uid="{C4DD00FB-4E4E-4EB6-8BB2-F344FFBC7CED}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
